--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\OpenSource\GF_X\AAAGameData\Configs\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{410A1752-D60B-406D-9E65-C4B088B14C00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="1005" yWindow="6165" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="29100" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,13 +14,26 @@
   <definedNames>
     <definedName name="GameConfig" localSheetId="0">Sheet1!$A$1:$D$5</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
-<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
-  <connection id="1" xr16:uid="{00000000-0015-0000-FFFF-FFFF00000000}" name="GameConfig" type="6" refreshedVersion="2" background="1" saveData="1">
+<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <connection id="1" name="GameConfig" type="6" background="1" refreshedVersion="2" saveData="1">
     <textPr sourceFile="C:\Workspace\UnityProjects\Gold Digger\DataTables\GameConfig.txt">
       <textFields>
         <textField/>
@@ -37,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
   <si>
     <t>#</t>
   </si>
@@ -45,10 +52,22 @@
     <t>默认游戏配置</t>
   </si>
   <si>
+    <t>Key</t>
+  </si>
+  <si>
     <t>备注</t>
   </si>
   <si>
     <t>Value</t>
+  </si>
+  <si>
+    <t>DefaultCoins</t>
+  </si>
+  <si>
+    <t>玩家初始金币数</t>
+  </si>
+  <si>
+    <t>DefaultDiamonds</t>
   </si>
   <si>
     <t>APPSTORE</t>
@@ -60,70 +79,374 @@
     <t>https://apps.apple.com/</t>
   </si>
   <si>
-    <t>Key</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>DefaultCoins</t>
-  </si>
-  <si>
-    <t>DefaultDiamonds</t>
-  </si>
-  <si>
-    <t>玩家初始金币数</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>玩家初始金币数</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>DisplayRotation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -131,10 +454,249 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -142,30 +704,73 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="超链接" xfId="1" builtinId="8"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="GameConfig" connectionId="1" xr16:uid="{00000000-0016-0000-0000-000000000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="GameConfig" connectionId="1" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -449,14 +1054,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.8" outlineLevelRow="5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="2" width="35" customWidth="1"/>
@@ -464,7 +1069,7 @@
     <col min="4" max="4" width="26.125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -472,79 +1077,89 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>7</v>
+      <c r="B2" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:4">
       <c r="B3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D3" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:4">
       <c r="B4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D4" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:4">
       <c r="B5" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4">
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="1">
+        <v>38.7</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D5" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D5" r:id="rId1" display="https://apps.apple.com/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.8"/>
   <sheetData/>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.8"/>
   <sheetData/>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="13380"/>
+    <workbookView windowWidth="25600" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t>#</t>
   </si>
@@ -61,25 +61,34 @@
     <t>Value</t>
   </si>
   <si>
-    <t>DefaultCoins</t>
-  </si>
-  <si>
-    <t>玩家初始金币数</t>
-  </si>
-  <si>
-    <t>DefaultDiamonds</t>
-  </si>
-  <si>
-    <t>APPSTORE</t>
-  </si>
-  <si>
-    <t>苹果商店评分跳转连接</t>
-  </si>
-  <si>
-    <t>https://apps.apple.com/</t>
-  </si>
-  <si>
-    <t>DisplayRotation</t>
+    <t>MinAtkSpeed</t>
+  </si>
+  <si>
+    <t>攻速下限</t>
+  </si>
+  <si>
+    <t>MaxAtkSpeed</t>
+  </si>
+  <si>
+    <t>攻速上限</t>
+  </si>
+  <si>
+    <t>MinMoveSpeed</t>
+  </si>
+  <si>
+    <t>移速下限</t>
+  </si>
+  <si>
+    <t>MaxMoveSpeed</t>
+  </si>
+  <si>
+    <t>移速上限</t>
+  </si>
+  <si>
+    <t>DistanceConversionRate</t>
+  </si>
+  <si>
+    <t>距离码数转换为unity距离的比例</t>
   </si>
 </sst>
 </file>
@@ -87,46 +96,39 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -134,7 +136,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -142,7 +144,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -150,7 +152,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -158,7 +160,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -166,14 +168,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -181,7 +183,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -189,7 +191,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -197,14 +199,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -212,42 +214,42 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -555,210 +557,207 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1060,16 +1059,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.8" outlineLevelRow="5" outlineLevelCol="3"/>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultColWidth="8.87272727272727" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="3" width="51.125" customWidth="1"/>
-    <col min="4" max="4" width="26.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="51.1272727272727" customWidth="1"/>
+    <col min="4" max="4" width="26.1272727272727" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1091,7 +1090,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="2:4">
+    <row r="3" spans="1:4">
       <c r="B3" t="s">
         <v>5</v>
       </c>
@@ -1099,43 +1098,54 @@
         <v>6</v>
       </c>
       <c r="D3" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="4" spans="2:4">
+    <row r="4" spans="1:4">
       <c r="B4" t="s">
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D4" s="1">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="2:4">
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4">
+    <row r="6" spans="1:4">
       <c r="B6" t="s">
         <v>11</v>
       </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
       <c r="D6" s="1">
-        <v>38.7</v>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D5" r:id="rId1" display="https://apps.apple.com/"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter/>
@@ -1146,7 +1156,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="8.87272727272727" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -1157,7 +1167,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="8.87272727272727" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="10480"/>
+    <workbookView windowWidth="19200" windowHeight="8200"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>#</t>
   </si>
@@ -89,6 +89,24 @@
   </si>
   <si>
     <t>距离码数转换为unity距离的比例</t>
+  </si>
+  <si>
+    <t>SmallUnitCollisionRadius</t>
+  </si>
+  <si>
+    <t>小型单位碰撞半径</t>
+  </si>
+  <si>
+    <t>MediumUnitCollisionRadius</t>
+  </si>
+  <si>
+    <t>中型单位碰撞半径</t>
+  </si>
+  <si>
+    <t>LargeUnitCollisionRadius</t>
+  </si>
+  <si>
+    <t>大型单位碰撞半径</t>
   </si>
 </sst>
 </file>
@@ -1059,8 +1077,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultColWidth="8.87272727272727" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="3"/>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultColWidth="8.87272727272727" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="2" width="35" customWidth="1"/>
@@ -1068,7 +1086,7 @@
     <col min="4" max="4" width="26.1272727272727" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1090,7 +1108,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="2:4">
       <c r="B3" t="s">
         <v>5</v>
       </c>
@@ -1101,7 +1119,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="2:4">
       <c r="B4" t="s">
         <v>7</v>
       </c>
@@ -1112,7 +1130,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="2:4">
       <c r="B5" t="s">
         <v>9</v>
       </c>
@@ -1123,7 +1141,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="2:4">
       <c r="B6" t="s">
         <v>11</v>
       </c>
@@ -1134,7 +1152,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="2:4">
       <c r="B7" t="s">
         <v>13</v>
       </c>
@@ -1143,6 +1161,39 @@
       </c>
       <c r="D7" s="1">
         <v>0.02</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4">
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4">
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4">
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="1">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8200"/>
+    <workbookView windowWidth="25600" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>#</t>
   </si>
@@ -107,6 +107,12 @@
   </si>
   <si>
     <t>大型单位碰撞半径</t>
+  </si>
+  <si>
+    <t>DiscardResourceConversionRate</t>
+  </si>
+  <si>
+    <t>弃牌时转化资源量与人口之比</t>
   </si>
 </sst>
 </file>
@@ -1077,7 +1083,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultColWidth="8.87272727272727" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
@@ -1086,7 +1092,7 @@
     <col min="4" max="4" width="26.1272727272727" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1108,7 +1114,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="2:4">
+    <row r="3" spans="1:4">
       <c r="B3" t="s">
         <v>5</v>
       </c>
@@ -1119,7 +1125,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="2:4">
+    <row r="4" spans="1:4">
       <c r="B4" t="s">
         <v>7</v>
       </c>
@@ -1130,7 +1136,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="5" spans="2:4">
+    <row r="5" spans="1:4">
       <c r="B5" t="s">
         <v>9</v>
       </c>
@@ -1141,7 +1147,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="2:4">
+    <row r="6" spans="1:4">
       <c r="B6" t="s">
         <v>11</v>
       </c>
@@ -1152,7 +1158,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="2:4">
+    <row r="7" spans="1:4">
       <c r="B7" t="s">
         <v>13</v>
       </c>
@@ -1163,7 +1169,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="8" spans="2:4">
+    <row r="8" spans="1:4">
       <c r="B8" t="s">
         <v>15</v>
       </c>
@@ -1174,7 +1180,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="2:4">
+    <row r="9" spans="1:4">
       <c r="B9" t="s">
         <v>17</v>
       </c>
@@ -1185,7 +1191,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="2:4">
+    <row r="10" spans="1:4">
       <c r="B10" t="s">
         <v>19</v>
       </c>
@@ -1194,6 +1200,17 @@
       </c>
       <c r="D10" s="1">
         <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="1">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
   <si>
     <t>#</t>
   </si>
@@ -113,6 +113,18 @@
   </si>
   <si>
     <t>弃牌时转化资源量与人口之比</t>
+  </si>
+  <si>
+    <t>InitMaxSupply</t>
+  </si>
+  <si>
+    <t>初始人口上限</t>
+  </si>
+  <si>
+    <t>BaseProvideSupply</t>
+  </si>
+  <si>
+    <t>每个基地每级提供的人口上限</t>
   </si>
 </sst>
 </file>
@@ -1083,7 +1095,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultColWidth="8.87272727272727" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
@@ -1211,6 +1223,28 @@
       </c>
       <c r="D11" s="1">
         <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="1">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8200"/>
+    <workbookView windowWidth="25600" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
   <si>
     <t>#</t>
   </si>
@@ -143,6 +143,12 @@
   </si>
   <si>
     <t>建筑视野</t>
+  </si>
+  <si>
+    <t>KillRewardSupplyRatio</t>
+  </si>
+  <si>
+    <t>击杀人口与奖励资源之比</t>
   </si>
 </sst>
 </file>
@@ -1113,7 +1119,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultColWidth="8.87272727272727" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
@@ -1122,7 +1128,7 @@
     <col min="4" max="4" width="26.1272727272727" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1144,7 +1150,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="2:4">
+    <row r="3" spans="1:4">
       <c r="B3" t="s">
         <v>5</v>
       </c>
@@ -1155,7 +1161,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="2:4">
+    <row r="4" spans="1:4">
       <c r="B4" t="s">
         <v>7</v>
       </c>
@@ -1166,7 +1172,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="5" spans="2:4">
+    <row r="5" spans="1:4">
       <c r="B5" t="s">
         <v>9</v>
       </c>
@@ -1177,7 +1183,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="2:4">
+    <row r="6" spans="1:4">
       <c r="B6" t="s">
         <v>11</v>
       </c>
@@ -1188,7 +1194,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="2:4">
+    <row r="7" spans="1:4">
       <c r="B7" t="s">
         <v>13</v>
       </c>
@@ -1199,7 +1205,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="8" spans="2:4">
+    <row r="8" spans="1:4">
       <c r="B8" t="s">
         <v>15</v>
       </c>
@@ -1207,10 +1213,10 @@
         <v>16</v>
       </c>
       <c r="D8" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="B9" t="s">
         <v>17</v>
       </c>
@@ -1218,10 +1224,10 @@
         <v>18</v>
       </c>
       <c r="D9" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="B10" t="s">
         <v>19</v>
       </c>
@@ -1229,10 +1235,10 @@
         <v>20</v>
       </c>
       <c r="D10" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="B11" t="s">
         <v>21</v>
       </c>
@@ -1243,7 +1249,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="2:4">
+    <row r="12" spans="1:4">
       <c r="B12" t="s">
         <v>23</v>
       </c>
@@ -1254,7 +1260,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="2:4">
+    <row r="13" spans="1:4">
       <c r="B13" t="s">
         <v>25</v>
       </c>
@@ -1265,7 +1271,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="2:4">
+    <row r="14" spans="1:4">
       <c r="B14" t="s">
         <v>27</v>
       </c>
@@ -1276,7 +1282,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="15" spans="2:4">
+    <row r="15" spans="1:4">
       <c r="B15" t="s">
         <v>29</v>
       </c>
@@ -1287,7 +1293,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="16" spans="2:4">
+    <row r="16" spans="1:4">
       <c r="B16" t="s">
         <v>31</v>
       </c>
@@ -1296,6 +1302,17 @@
       </c>
       <c r="D16" s="1">
         <v>900</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4">
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" s="1">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="10480"/>
+    <workbookView windowWidth="19200" windowHeight="8200"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1128,7 +1128,7 @@
     <col min="4" max="4" width="26.1272727272727" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1150,7 +1150,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="2:4">
       <c r="B3" t="s">
         <v>5</v>
       </c>
@@ -1161,7 +1161,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="2:4">
       <c r="B4" t="s">
         <v>7</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="2:4">
       <c r="B5" t="s">
         <v>9</v>
       </c>
@@ -1183,7 +1183,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="2:4">
       <c r="B6" t="s">
         <v>11</v>
       </c>
@@ -1194,7 +1194,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="2:4">
       <c r="B7" t="s">
         <v>13</v>
       </c>
@@ -1202,10 +1202,10 @@
         <v>14</v>
       </c>
       <c r="D7" s="1">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4">
       <c r="B8" t="s">
         <v>15</v>
       </c>
@@ -1213,10 +1213,10 @@
         <v>16</v>
       </c>
       <c r="D8" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4">
       <c r="B9" t="s">
         <v>17</v>
       </c>
@@ -1224,10 +1224,10 @@
         <v>18</v>
       </c>
       <c r="D9" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4">
       <c r="B10" t="s">
         <v>19</v>
       </c>
@@ -1235,10 +1235,10 @@
         <v>20</v>
       </c>
       <c r="D10" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4">
       <c r="B11" t="s">
         <v>21</v>
       </c>
@@ -1249,7 +1249,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="2:4">
       <c r="B12" t="s">
         <v>23</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="2:4">
       <c r="B13" t="s">
         <v>25</v>
       </c>
@@ -1271,7 +1271,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="2:4">
       <c r="B14" t="s">
         <v>27</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="2:4">
       <c r="B15" t="s">
         <v>29</v>
       </c>
@@ -1293,7 +1293,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="2:4">
       <c r="B16" t="s">
         <v>31</v>
       </c>

--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8200"/>
+    <workbookView windowWidth="25600" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1128,7 +1128,7 @@
     <col min="4" max="4" width="26.1272727272727" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1150,7 +1150,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="2:4">
+    <row r="3" spans="1:4">
       <c r="B3" t="s">
         <v>5</v>
       </c>
@@ -1161,7 +1161,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="2:4">
+    <row r="4" spans="1:4">
       <c r="B4" t="s">
         <v>7</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="5" spans="2:4">
+    <row r="5" spans="1:4">
       <c r="B5" t="s">
         <v>9</v>
       </c>
@@ -1183,7 +1183,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="2:4">
+    <row r="6" spans="1:4">
       <c r="B6" t="s">
         <v>11</v>
       </c>
@@ -1194,7 +1194,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="2:4">
+    <row r="7" spans="1:4">
       <c r="B7" t="s">
         <v>13</v>
       </c>
@@ -1205,7 +1205,7 @@
         <v>0.015</v>
       </c>
     </row>
-    <row r="8" spans="2:4">
+    <row r="8" spans="1:4">
       <c r="B8" t="s">
         <v>15</v>
       </c>
@@ -1216,7 +1216,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="2:4">
+    <row r="9" spans="1:4">
       <c r="B9" t="s">
         <v>17</v>
       </c>
@@ -1227,7 +1227,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:4">
+    <row r="10" spans="1:4">
       <c r="B10" t="s">
         <v>19</v>
       </c>
@@ -1235,10 +1235,10 @@
         <v>20</v>
       </c>
       <c r="D10" s="1">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="B11" t="s">
         <v>21</v>
       </c>
@@ -1249,7 +1249,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="2:4">
+    <row r="12" spans="1:4">
       <c r="B12" t="s">
         <v>23</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="2:4">
+    <row r="13" spans="1:4">
       <c r="B13" t="s">
         <v>25</v>
       </c>
@@ -1271,7 +1271,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="2:4">
+    <row r="14" spans="1:4">
       <c r="B14" t="s">
         <v>27</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="15" spans="2:4">
+    <row r="15" spans="1:4">
       <c r="B15" t="s">
         <v>29</v>
       </c>
@@ -1293,7 +1293,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="16" spans="2:4">
+    <row r="16" spans="1:4">
       <c r="B16" t="s">
         <v>31</v>
       </c>

--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -1213,7 +1213,7 @@
         <v>16</v>
       </c>
       <c r="D8" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1224,7 +1224,7 @@
         <v>18</v>
       </c>
       <c r="D9" s="1">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1235,7 +1235,7 @@
         <v>20</v>
       </c>
       <c r="D10" s="1">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:4">

--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -11,9 +11,6 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName name="GameConfig" localSheetId="0">Sheet1!$A$1:$D$5</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -31,20 +28,8 @@
 </workbook>
 </file>
 
-<file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
-<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <connection id="1" name="GameConfig" type="6" background="1" refreshedVersion="2" saveData="1">
-    <textPr sourceFile="C:\Workspace\UnityProjects\Gold Digger\DataTables\GameConfig.txt">
-      <textFields>
-        <textField/>
-      </textFields>
-    </textPr>
-  </connection>
-</connections>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="61">
   <si>
     <t>#</t>
   </si>
@@ -94,7 +79,7 @@
     <t>SmallUnitCollisionRadius</t>
   </si>
   <si>
-    <t>小型单位碰撞半径</t>
+    <t>轻型单位碰撞半径</t>
   </si>
   <si>
     <t>MediumUnitCollisionRadius</t>
@@ -106,7 +91,13 @@
     <t>LargeUnitCollisionRadius</t>
   </si>
   <si>
-    <t>大型单位碰撞半径</t>
+    <t>重型单位碰撞半径</t>
+  </si>
+  <si>
+    <t>SuperLargeUnitCollisionRadius</t>
+  </si>
+  <si>
+    <t>超重型单位碰撞半径</t>
   </si>
   <si>
     <t>DiscardResourceConversionRate</t>
@@ -149,6 +140,78 @@
   </si>
   <si>
     <t>击杀人口与奖励资源之比</t>
+  </si>
+  <si>
+    <t>ResourcePointInitialAmount</t>
+  </si>
+  <si>
+    <t>资源点初始资源量</t>
+  </si>
+  <si>
+    <t>BuildingRecycleRefundRate</t>
+  </si>
+  <si>
+    <t>回收建筑返还资源百分比</t>
+  </si>
+  <si>
+    <t>BaseCriticalDamageRate</t>
+  </si>
+  <si>
+    <t>基础暴击伤害百分比</t>
+  </si>
+  <si>
+    <t>MinimumDamagePerHit</t>
+  </si>
+  <si>
+    <t>单次伤害下限</t>
+  </si>
+  <si>
+    <t>KnockbackForceLevel0</t>
+  </si>
+  <si>
+    <t>0级推力</t>
+  </si>
+  <si>
+    <t>KnockbackForceLevel1</t>
+  </si>
+  <si>
+    <t>1级推力</t>
+  </si>
+  <si>
+    <t>KnockbackForceLevel2</t>
+  </si>
+  <si>
+    <t>2级推力</t>
+  </si>
+  <si>
+    <t>KnockbackForceLevel3</t>
+  </si>
+  <si>
+    <t>3级推力</t>
+  </si>
+  <si>
+    <t>PullForceLevel0</t>
+  </si>
+  <si>
+    <t>0级拉力</t>
+  </si>
+  <si>
+    <t>PullForceLevel1</t>
+  </si>
+  <si>
+    <t>1级拉力</t>
+  </si>
+  <si>
+    <t>PullForceLevel2</t>
+  </si>
+  <si>
+    <t>2级拉力</t>
+  </si>
+  <si>
+    <t>PullForceLevel3</t>
+  </si>
+  <si>
+    <t>3级拉力</t>
   </si>
 </sst>
 </file>
@@ -157,11 +220,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -170,11 +233,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
-      <color theme="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -616,157 +685,166 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -819,7 +897,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -828,14 +906,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="GameConfig" connectionId="1" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="WPS">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -843,39 +917,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4874CB"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="EE822F"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="F2BA02"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="75BD42"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="30C0B4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="E54C5E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0026E5"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="7E1FAD"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="WPS">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -945,169 +1019,132 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="WPS">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumOff val="17500"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
+              <a:schemeClr val="phClr"/>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="2700000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:hueOff val="-2520000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
+              <a:schemeClr val="phClr"/>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="2700000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:gradFill>
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="phClr">
+                  <a:hueOff val="-4200000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="phClr"/>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="2700000" scaled="1"/>
+          </a:gradFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
+            <a:outerShdw blurRad="101600" dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:schemeClr val="phClr">
+                <a:alpha val="60000"/>
+              </a:schemeClr>
             </a:outerShdw>
           </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
+            <a:reflection stA="50000" endA="300" endPos="40000" dist="25400" dir="5400000" sy="-100000" algn="bl" rotWithShape="0"/>
           </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -1119,205 +1156,364 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultColWidth="8.87272727272727" defaultRowHeight="14" outlineLevelCol="3"/>
+  <dimension ref="A1:D30"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="2.5" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="3" width="51.1272727272727" customWidth="1"/>
-    <col min="4" max="4" width="26.1272727272727" style="1" customWidth="1"/>
+    <col min="2" max="2" width="33.3636363636364" customWidth="1"/>
+    <col min="3" max="3" width="36.3636363636364" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="2"/>
+      <c r="D1" s="3"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="B3" t="s">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="3">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="B4" t="s">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="3">
         <v>700</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="B5" t="s">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="3">
         <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="B6" t="s">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="3">
         <v>1000</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="B7" t="s">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="3">
         <v>0.015</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="B8" t="s">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="3">
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="B9" t="s">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="3">
         <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="B10" t="s">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="3">
         <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="B11" t="s">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
-      <c r="B12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="1">
+    <row r="13" spans="1:4">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
-      <c r="B13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" s="1">
+    <row r="14" spans="1:4">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
-      <c r="B14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" s="1">
+    <row r="15" spans="1:4">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
-      <c r="B15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" s="1">
+    <row r="16" spans="1:4">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
-      <c r="B16" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" s="1">
+    <row r="17" spans="1:4">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="17" spans="2:4">
-      <c r="B17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" t="s">
-        <v>34</v>
-      </c>
-      <c r="D17" s="1">
+    <row r="18" spans="1:4">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="3">
         <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" t="s">
+        <v>38</v>
+      </c>
+      <c r="D19" s="4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="B20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="B21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" t="s">
+        <v>42</v>
+      </c>
+      <c r="D21" s="4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="B22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="B23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" t="s">
+        <v>46</v>
+      </c>
+      <c r="D23" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="B24" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" t="s">
+        <v>48</v>
+      </c>
+      <c r="D24" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="B25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="B26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" t="s">
+        <v>52</v>
+      </c>
+      <c r="D26" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="B27" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" t="s">
+        <v>54</v>
+      </c>
+      <c r="D27" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="B28" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" t="s">
+        <v>56</v>
+      </c>
+      <c r="D28" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="B29" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" t="s">
+        <v>58</v>
+      </c>
+      <c r="D29" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="B30" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30" t="s">
+        <v>60</v>
+      </c>
+      <c r="D30" s="4">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -1326,9 +1522,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.87272727272727" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -1337,9 +1534,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.87272727272727" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="75">
   <si>
     <t>#</t>
   </si>
@@ -230,6 +230,30 @@
   </si>
   <si>
     <t>防御阶段无尽出怪增长率</t>
+  </si>
+  <si>
+    <t>BaseResourceIncomeDailyGrowth</t>
+  </si>
+  <si>
+    <t>基础资源收获每日增长量</t>
+  </si>
+  <si>
+    <t>DefendPhaseBaseResourceIncome</t>
+  </si>
+  <si>
+    <t>防御阶段基础资源收获</t>
+  </si>
+  <si>
+    <t>InvadePhaseIncomePerCapturedOutpost</t>
+  </si>
+  <si>
+    <t>进攻阶段每个占领据点提供资源收获</t>
+  </si>
+  <si>
+    <t>EnemyProductionBuildingDailyResourceCost</t>
+  </si>
+  <si>
+    <t>敌方生产建筑每日消耗资源量</t>
   </si>
 </sst>
 </file>
@@ -1174,7 +1198,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="33.3636363636364" customWidth="1"/>
@@ -1560,6 +1584,50 @@
       </c>
       <c r="D33">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4">
+      <c r="B34" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" t="s">
+        <v>68</v>
+      </c>
+      <c r="D34">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4">
+      <c r="B35" t="s">
+        <v>69</v>
+      </c>
+      <c r="C35" t="s">
+        <v>70</v>
+      </c>
+      <c r="D35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4">
+      <c r="B36" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" t="s">
+        <v>72</v>
+      </c>
+      <c r="D36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4">
+      <c r="B37" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" t="s">
+        <v>74</v>
+      </c>
+      <c r="D37">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="77">
   <si>
     <t>#</t>
   </si>
@@ -254,6 +254,12 @@
   </si>
   <si>
     <t>敌方生产建筑每日消耗资源量</t>
+  </si>
+  <si>
+    <t>LvTagPositiveMaxCount</t>
+  </si>
+  <si>
+    <t>关卡正面tag选择数量上限</t>
   </si>
 </sst>
 </file>
@@ -1198,7 +1204,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="33.3636363636364" customWidth="1"/>
@@ -1627,6 +1633,17 @@
         <v>74</v>
       </c>
       <c r="D37">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4">
+      <c r="B38" t="s">
+        <v>75</v>
+      </c>
+      <c r="C38" t="s">
+        <v>76</v>
+      </c>
+      <c r="D38">
         <v>3</v>
       </c>
     </row>

--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="79">
   <si>
     <t>#</t>
   </si>
@@ -166,6 +166,12 @@
     <t>单次伤害下限</t>
   </si>
   <si>
+    <t>KnockbackForceLevelM1</t>
+  </si>
+  <si>
+    <t>-1级推力</t>
+  </si>
+  <si>
     <t>KnockbackForceLevel0</t>
   </si>
   <si>
@@ -175,19 +181,13 @@
     <t>KnockbackForceLevel1</t>
   </si>
   <si>
-    <t>1级推力</t>
-  </si>
-  <si>
-    <t>KnockbackForceLevel2</t>
-  </si>
-  <si>
-    <t>2级推力</t>
-  </si>
-  <si>
-    <t>KnockbackForceLevel3</t>
-  </si>
-  <si>
-    <t>3级推力</t>
+    <t>1级及以上推力</t>
+  </si>
+  <si>
+    <t>PullForceLevelM1</t>
+  </si>
+  <si>
+    <t>-1级拉力</t>
   </si>
   <si>
     <t>PullForceLevel0</t>
@@ -199,19 +199,25 @@
     <t>PullForceLevel1</t>
   </si>
   <si>
-    <t>1级拉力</t>
-  </si>
-  <si>
-    <t>PullForceLevel2</t>
-  </si>
-  <si>
-    <t>2级拉力</t>
-  </si>
-  <si>
-    <t>PullForceLevel3</t>
-  </si>
-  <si>
-    <t>3级拉力</t>
+    <t>1级及以上拉力</t>
+  </si>
+  <si>
+    <t>PullDurationLevelM1</t>
+  </si>
+  <si>
+    <t>-1级拉力作用时间</t>
+  </si>
+  <si>
+    <t>PullDurationLevel0</t>
+  </si>
+  <si>
+    <t>0级及以上拉力作用时间</t>
+  </si>
+  <si>
+    <t>Friction</t>
+  </si>
+  <si>
+    <t>摩擦力</t>
   </si>
   <si>
     <t>DefendPhaseEnemyArriveInterval</t>
@@ -892,6 +898,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1204,7 +1213,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="33.3636363636364" customWidth="1"/>
@@ -1475,11 +1484,11 @@
       <c r="B23" t="s">
         <v>45</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D23" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1490,7 +1499,7 @@
         <v>48</v>
       </c>
       <c r="D24" s="4">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1501,18 +1510,18 @@
         <v>50</v>
       </c>
       <c r="D25" s="4">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="B26" t="s">
         <v>51</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="5" t="s">
         <v>52</v>
       </c>
       <c r="D26" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1523,7 +1532,7 @@
         <v>54</v>
       </c>
       <c r="D27" s="4">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1534,21 +1543,21 @@
         <v>56</v>
       </c>
       <c r="D28" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" customFormat="1" spans="1:4">
       <c r="B29" t="s">
         <v>57</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="5" t="s">
         <v>58</v>
       </c>
       <c r="D29" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="30" customFormat="1" spans="1:4">
       <c r="B30" t="s">
         <v>59</v>
       </c>
@@ -1556,7 +1565,7 @@
         <v>60</v>
       </c>
       <c r="D30" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1567,7 +1576,7 @@
         <v>62</v>
       </c>
       <c r="D31">
-        <v>0.8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1578,7 +1587,7 @@
         <v>64</v>
       </c>
       <c r="D32">
-        <v>500</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="33" spans="2:4">
@@ -1589,7 +1598,7 @@
         <v>66</v>
       </c>
       <c r="D33">
-        <v>1.2</v>
+        <v>500</v>
       </c>
     </row>
     <row r="34" spans="2:4">
@@ -1600,7 +1609,7 @@
         <v>68</v>
       </c>
       <c r="D34">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="35" spans="2:4">
@@ -1611,7 +1620,7 @@
         <v>70</v>
       </c>
       <c r="D35">
-        <v>3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="36" spans="2:4">
@@ -1622,7 +1631,7 @@
         <v>72</v>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="2:4">
@@ -1633,7 +1642,7 @@
         <v>74</v>
       </c>
       <c r="D37">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="2:4">
@@ -1644,6 +1653,17 @@
         <v>76</v>
       </c>
       <c r="D38">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4">
+      <c r="B39" t="s">
+        <v>77</v>
+      </c>
+      <c r="C39" t="s">
+        <v>78</v>
+      </c>
+      <c r="D39">
         <v>3</v>
       </c>
     </row>

--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\Avenge\AAAGameData\Configs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="25600" windowHeight="10480"/>
   </bookViews>
@@ -1488,7 +1493,7 @@
         <v>46</v>
       </c>
       <c r="D23" s="4">
-        <v>3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1499,7 +1504,7 @@
         <v>48</v>
       </c>
       <c r="D24" s="4">
-        <v>8</v>
+        <v>300</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1510,7 +1515,7 @@
         <v>50</v>
       </c>
       <c r="D25" s="4">
-        <v>12</v>
+        <v>450</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1521,7 +1526,7 @@
         <v>52</v>
       </c>
       <c r="D26" s="4">
-        <v>5</v>
+        <v>200</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1532,7 +1537,7 @@
         <v>54</v>
       </c>
       <c r="D27" s="4">
-        <v>25</v>
+        <v>800</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1543,7 +1548,7 @@
         <v>56</v>
       </c>
       <c r="D28" s="4">
-        <v>100</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="29" customFormat="1" spans="1:4">
@@ -1576,7 +1581,7 @@
         <v>62</v>
       </c>
       <c r="D31">
-        <v>12</v>
+        <v>400</v>
       </c>
     </row>
     <row r="32" spans="1:4">

--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="81">
   <si>
     <t>#</t>
   </si>
@@ -271,6 +271,12 @@
   </si>
   <si>
     <t>关卡正面tag选择数量上限</t>
+  </si>
+  <si>
+    <t>OffsetRateExpCoefficient</t>
+  </si>
+  <si>
+    <t>偏移率提供的经验获取系数</t>
   </si>
 </sst>
 </file>
@@ -1218,7 +1224,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="33.3636363636364" customWidth="1"/>
@@ -1670,6 +1676,17 @@
       </c>
       <c r="D39">
         <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4">
+      <c r="B40" t="s">
+        <v>79</v>
+      </c>
+      <c r="C40" t="s">
+        <v>80</v>
+      </c>
+      <c r="D40">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="83">
   <si>
     <t>#</t>
   </si>
@@ -277,6 +277,12 @@
   </si>
   <si>
     <t>偏移率提供的经验获取系数</t>
+  </si>
+  <si>
+    <t>OffsetRateRequiredForGrowthPoint</t>
+  </si>
+  <si>
+    <t>获取局外成长点数所需的合约等级</t>
   </si>
 </sst>
 </file>
@@ -1224,7 +1230,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="33.3636363636364" customWidth="1"/>
@@ -1687,6 +1693,17 @@
       </c>
       <c r="D40">
         <v>0.1</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4">
+      <c r="B41" t="s">
+        <v>81</v>
+      </c>
+      <c r="C41" t="s">
+        <v>82</v>
+      </c>
+      <c r="D41">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="95">
   <si>
     <t>#</t>
   </si>
@@ -283,6 +283,42 @@
   </si>
   <si>
     <t>获取局外成长点数所需的合约等级</t>
+  </si>
+  <si>
+    <t>OffsetBadgeBronzeThreshold</t>
+  </si>
+  <si>
+    <t>关卡偏移率铜角标阈值</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>OffsetBadgeSilverThreshold</t>
+  </si>
+  <si>
+    <t>关卡偏移率银角标阈值</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>OffsetBadgeGoldThreshold</t>
+  </si>
+  <si>
+    <t>关卡偏移率金角标阈值</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>OffsetBadgeDiamondThreshold</t>
+  </si>
+  <si>
+    <t>关卡偏移率钻角标阈值</t>
+  </si>
+  <si>
+    <t>28</t>
   </si>
 </sst>
 </file>
@@ -1230,7 +1266,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="33.3636363636364" customWidth="1"/>
@@ -1692,18 +1728,51 @@
         <v>80</v>
       </c>
       <c r="D40">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C41" t="s">
-        <v>82</v>
-      </c>
-      <c r="D41">
-        <v>10</v>
+        <v>84</v>
+      </c>
+      <c r="D41" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4">
+      <c r="B42" t="s">
+        <v>86</v>
+      </c>
+      <c r="C42" t="s">
+        <v>87</v>
+      </c>
+      <c r="D42" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4">
+      <c r="B43" t="s">
+        <v>89</v>
+      </c>
+      <c r="C43" t="s">
+        <v>90</v>
+      </c>
+      <c r="D43" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4">
+      <c r="B44" t="s">
+        <v>92</v>
+      </c>
+      <c r="C44" t="s">
+        <v>93</v>
+      </c>
+      <c r="D44" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="97">
   <si>
     <t>#</t>
   </si>
@@ -279,12 +279,6 @@
     <t>偏移率提供的经验获取系数</t>
   </si>
   <si>
-    <t>OffsetRateRequiredForGrowthPoint</t>
-  </si>
-  <si>
-    <t>获取局外成长点数所需的合约等级</t>
-  </si>
-  <si>
     <t>OffsetBadgeBronzeThreshold</t>
   </si>
   <si>
@@ -319,6 +313,18 @@
   </si>
   <si>
     <t>28</t>
+  </si>
+  <si>
+    <t>TauntAdditionalPursuitDistance</t>
+  </si>
+  <si>
+    <t>嘲讽额外追击距离</t>
+  </si>
+  <si>
+    <t>TauntThreatPerLevel</t>
+  </si>
+  <si>
+    <t>嘲讽每级仇恨值</t>
   </si>
 </sst>
 </file>
@@ -1266,7 +1272,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="33.3636363636364" customWidth="1"/>
@@ -1733,46 +1739,68 @@
     </row>
     <row r="41" spans="2:4">
       <c r="B41" t="s">
+        <v>81</v>
+      </c>
+      <c r="C41" t="s">
+        <v>82</v>
+      </c>
+      <c r="D41" t="s">
         <v>83</v>
-      </c>
-      <c r="C41" t="s">
-        <v>84</v>
-      </c>
-      <c r="D41" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" t="s">
+        <v>84</v>
+      </c>
+      <c r="C42" t="s">
+        <v>85</v>
+      </c>
+      <c r="D42" t="s">
         <v>86</v>
-      </c>
-      <c r="C42" t="s">
-        <v>87</v>
-      </c>
-      <c r="D42" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" t="s">
+        <v>87</v>
+      </c>
+      <c r="C43" t="s">
+        <v>88</v>
+      </c>
+      <c r="D43" t="s">
         <v>89</v>
-      </c>
-      <c r="C43" t="s">
-        <v>90</v>
-      </c>
-      <c r="D43" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" t="s">
+        <v>90</v>
+      </c>
+      <c r="C44" t="s">
+        <v>91</v>
+      </c>
+      <c r="D44" t="s">
         <v>92</v>
       </c>
-      <c r="C44" t="s">
+    </row>
+    <row r="45" spans="2:4">
+      <c r="B45" t="s">
         <v>93</v>
       </c>
-      <c r="D44" t="s">
+      <c r="C45" t="s">
         <v>94</v>
+      </c>
+      <c r="D45">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4">
+      <c r="B46" t="s">
+        <v>95</v>
+      </c>
+      <c r="C46" t="s">
+        <v>96</v>
+      </c>
+      <c r="D46">
+        <v>10000</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="107">
   <si>
     <t>#</t>
   </si>
@@ -105,10 +105,22 @@
     <t>超重型单位碰撞半径</t>
   </si>
   <si>
-    <t>DiscardResourceConversionRate</t>
-  </si>
-  <si>
-    <t>弃牌时转化资源量与人口之比</t>
+    <t>DiscardResourceConversionLevel1</t>
+  </si>
+  <si>
+    <t>1级牌弃牌转化资源量</t>
+  </si>
+  <si>
+    <t>DiscardResourceConversionLevel2</t>
+  </si>
+  <si>
+    <t>2级牌弃牌转化资源量</t>
+  </si>
+  <si>
+    <t>DiscardResourceConversionLevel3</t>
+  </si>
+  <si>
+    <t>3级牌弃牌转化资源量</t>
   </si>
   <si>
     <t>InitMaxSupply</t>
@@ -153,12 +165,6 @@
     <t>资源点初始资源量</t>
   </si>
   <si>
-    <t>BuildingRecycleRefundRate</t>
-  </si>
-  <si>
-    <t>回收建筑返还资源百分比</t>
-  </si>
-  <si>
     <t>BaseCriticalDamageRate</t>
   </si>
   <si>
@@ -325,6 +331,30 @@
   </si>
   <si>
     <t>嘲讽每级仇恨值</t>
+  </si>
+  <si>
+    <t>BuildingExtraThreat</t>
+  </si>
+  <si>
+    <t>建筑额外仇恨值</t>
+  </si>
+  <si>
+    <t>DemolishedProdRevenueLossRate</t>
+  </si>
+  <si>
+    <t>生产建筑损毁当天损失收入百分比</t>
+  </si>
+  <si>
+    <t>DemolishEnemyProdReward</t>
+  </si>
+  <si>
+    <t>敌方生产建筑损毁提供奖励</t>
+  </si>
+  <si>
+    <t>CombatTeleportationWindUp</t>
+  </si>
+  <si>
+    <t>战斗阶段传送前摇</t>
   </si>
 </sst>
 </file>
@@ -798,167 +828,167 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" applyFont="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" applyFill="1" borderId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" applyFont="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" applyFont="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" applyFont="1" fillId="0" borderId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" applyFont="1" fillId="0" borderId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="3" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="3" applyFill="1" borderId="4" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="4" applyFill="1" borderId="5" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" applyFont="1" fillId="4" applyFill="1" borderId="4" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" applyFont="1" fillId="5" applyFill="1" borderId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" applyFont="1" fillId="0" borderId="7" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" applyFont="1" fillId="0" borderId="8" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" applyFont="1" fillId="6" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="7" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" applyFont="1" fillId="8" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" applyFont="1" fillId="9" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" applyFont="1" fillId="10" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" applyFont="1" fillId="11" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" applyFont="1" fillId="12" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" applyFont="1" fillId="13" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" applyFont="1" fillId="14" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" applyFont="1" fillId="15" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" applyFont="1" fillId="16" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" applyFont="1" fillId="17" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" applyFont="1" fillId="18" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" applyFont="1" fillId="19" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" applyFont="1" fillId="20" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" applyFont="1" fillId="21" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" applyFont="1" fillId="22" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" applyFont="1" fillId="23" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" applyFont="1" fillId="24" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" applyFont="1" fillId="25" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" applyFont="1" fillId="26" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" applyFont="1" fillId="27" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" applyFont="1" fillId="28" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" applyFont="1" fillId="29" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" applyFont="1" fillId="30" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" applyFont="1" fillId="31" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" applyFont="1" fillId="32" applyFill="1" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1272,14 +1302,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="33.3636363636364" customWidth="1"/>
     <col min="3" max="3" width="36.3636363636364" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1289,7 +1319,7 @@
       <c r="C1" s="2"/>
       <c r="D1" s="3"/>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1303,7 +1333,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3">
       <c r="A3" s="2"/>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -1315,7 +1345,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4">
       <c r="A4" s="2"/>
       <c r="B4" s="2" t="s">
         <v>7</v>
@@ -1327,7 +1357,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5">
       <c r="A5" s="2"/>
       <c r="B5" s="2" t="s">
         <v>9</v>
@@ -1339,7 +1369,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
         <v>11</v>
@@ -1351,7 +1381,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
         <v>13</v>
@@ -1363,7 +1393,7 @@
         <v>0.015</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8">
       <c r="A8" s="2"/>
       <c r="B8" s="2" t="s">
         <v>15</v>
@@ -1375,7 +1405,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
         <v>17</v>
@@ -1387,7 +1417,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
         <v>19</v>
@@ -1399,7 +1429,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
         <v>21</v>
@@ -1411,7 +1441,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12">
       <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
         <v>23</v>
@@ -1420,10 +1450,10 @@
         <v>24</v>
       </c>
       <c r="D12" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" s="2"/>
       <c r="B13" s="2" t="s">
         <v>25</v>
@@ -1432,10 +1462,10 @@
         <v>26</v>
       </c>
       <c r="D13" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" s="2"/>
       <c r="B14" s="2" t="s">
         <v>27</v>
@@ -1444,10 +1474,10 @@
         <v>28</v>
       </c>
       <c r="D14" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
         <v>29</v>
@@ -1456,10 +1486,10 @@
         <v>30</v>
       </c>
       <c r="D15" s="3">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" s="2"/>
       <c r="B16" s="2" t="s">
         <v>31</v>
@@ -1468,10 +1498,10 @@
         <v>32</v>
       </c>
       <c r="D16" s="3">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" s="2"/>
       <c r="B17" s="2" t="s">
         <v>33</v>
@@ -1480,10 +1510,10 @@
         <v>34</v>
       </c>
       <c r="D17" s="3">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" s="2"/>
       <c r="B18" s="2" t="s">
         <v>35</v>
@@ -1492,315 +1522,372 @@
         <v>36</v>
       </c>
       <c r="D18" s="3">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D19" s="3">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
-      <c r="B19" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" t="s">
-        <v>38</v>
-      </c>
-      <c r="D19" s="4">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="B20" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" t="s">
-        <v>40</v>
-      </c>
-      <c r="D20" s="4">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="B21" t="s">
+    <row r="21">
+      <c r="B21" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="0" t="s">
         <v>42</v>
       </c>
       <c r="D21" s="4">
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
-      <c r="B22" t="s">
+    <row r="22">
+      <c r="B22" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="0" t="s">
         <v>44</v>
       </c>
       <c r="D22" s="4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="D23" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
-      <c r="B23" t="s">
-        <v>45</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D23" s="4">
+    <row r="24">
+      <c r="B24" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D24" s="4">
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
-      <c r="B24" t="s">
-        <v>47</v>
-      </c>
-      <c r="C24" t="s">
-        <v>48</v>
-      </c>
-      <c r="D24" s="4">
+    <row r="25">
+      <c r="B25" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25" s="4">
         <v>300</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
-      <c r="B25" t="s">
-        <v>49</v>
-      </c>
-      <c r="C25" t="s">
+    <row r="26">
+      <c r="B26" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="D26" s="4">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D27" s="4">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="D28" s="4">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="D29" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D30" s="4">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="D31" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="D32" s="4">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="D33" s="4">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="D34" s="4">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="C35" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="D35" s="4">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="D36" s="4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="D37" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="C38" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="D38" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="C39" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="D39" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="C40" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="D40" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="C41" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="D41" s="4">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="C42" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="C43" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="C44" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="C45" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="C46" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="D46" s="4">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="C47" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="D47" s="4">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="C48" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="D48" s="4">
+        <v>-5000</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="C49" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="D49" s="4">
         <v>50</v>
       </c>
-      <c r="D25" s="4">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="B26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D26" s="4">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="B27" t="s">
-        <v>53</v>
-      </c>
-      <c r="C27" t="s">
-        <v>54</v>
-      </c>
-      <c r="D27" s="4">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="B28" t="s">
-        <v>55</v>
-      </c>
-      <c r="C28" t="s">
-        <v>56</v>
-      </c>
-      <c r="D28" s="4">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="29" customFormat="1" spans="1:4">
-      <c r="B29" t="s">
-        <v>57</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D29" s="4">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="30" customFormat="1" spans="1:4">
-      <c r="B30" t="s">
-        <v>59</v>
-      </c>
-      <c r="C30" t="s">
-        <v>60</v>
-      </c>
-      <c r="D30" s="4">
+    </row>
+    <row r="50">
+      <c r="B50" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="C50" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="D50" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="C51" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="D51" s="4">
         <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="B31" t="s">
-        <v>61</v>
-      </c>
-      <c r="C31" t="s">
-        <v>62</v>
-      </c>
-      <c r="D31">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="B32" t="s">
-        <v>63</v>
-      </c>
-      <c r="C32" t="s">
-        <v>64</v>
-      </c>
-      <c r="D32">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="33" spans="2:4">
-      <c r="B33" t="s">
-        <v>65</v>
-      </c>
-      <c r="C33" t="s">
-        <v>66</v>
-      </c>
-      <c r="D33">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="34" spans="2:4">
-      <c r="B34" t="s">
-        <v>67</v>
-      </c>
-      <c r="C34" t="s">
-        <v>68</v>
-      </c>
-      <c r="D34">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4">
-      <c r="B35" t="s">
-        <v>69</v>
-      </c>
-      <c r="C35" t="s">
-        <v>70</v>
-      </c>
-      <c r="D35">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="36" spans="2:4">
-      <c r="B36" t="s">
-        <v>71</v>
-      </c>
-      <c r="C36" t="s">
-        <v>72</v>
-      </c>
-      <c r="D36">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:4">
-      <c r="B37" t="s">
-        <v>73</v>
-      </c>
-      <c r="C37" t="s">
-        <v>74</v>
-      </c>
-      <c r="D37">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="2:4">
-      <c r="B38" t="s">
-        <v>75</v>
-      </c>
-      <c r="C38" t="s">
-        <v>76</v>
-      </c>
-      <c r="D38">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:4">
-      <c r="B39" t="s">
-        <v>77</v>
-      </c>
-      <c r="C39" t="s">
-        <v>78</v>
-      </c>
-      <c r="D39">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4">
-      <c r="B40" t="s">
-        <v>79</v>
-      </c>
-      <c r="C40" t="s">
-        <v>80</v>
-      </c>
-      <c r="D40">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="41" spans="2:4">
-      <c r="B41" t="s">
-        <v>81</v>
-      </c>
-      <c r="C41" t="s">
-        <v>82</v>
-      </c>
-      <c r="D41" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="42" spans="2:4">
-      <c r="B42" t="s">
-        <v>84</v>
-      </c>
-      <c r="C42" t="s">
-        <v>85</v>
-      </c>
-      <c r="D42" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4">
-      <c r="B43" t="s">
-        <v>87</v>
-      </c>
-      <c r="C43" t="s">
-        <v>88</v>
-      </c>
-      <c r="D43" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="44" spans="2:4">
-      <c r="B44" t="s">
-        <v>90</v>
-      </c>
-      <c r="C44" t="s">
-        <v>91</v>
-      </c>
-      <c r="D44" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="45" spans="2:4">
-      <c r="B45" t="s">
-        <v>93</v>
-      </c>
-      <c r="C45" t="s">
-        <v>94</v>
-      </c>
-      <c r="D45">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="46" spans="2:4">
-      <c r="B46" t="s">
-        <v>95</v>
-      </c>
-      <c r="C46" t="s">
-        <v>96</v>
-      </c>
-      <c r="D46">
-        <v>10000</v>
       </c>
     </row>
   </sheetData>
@@ -1813,7 +1900,6 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1825,7 +1911,6 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="109">
   <si>
     <t>#</t>
   </si>
@@ -355,6 +355,12 @@
   </si>
   <si>
     <t>战斗阶段传送前摇</t>
+  </si>
+  <si>
+    <t>VisionLossDelay</t>
+  </si>
+  <si>
+    <t>视野消失延迟</t>
   </si>
 </sst>
 </file>
@@ -828,167 +834,167 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" applyFont="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" applyFill="1" borderId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" applyFont="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" applyFont="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" applyFont="1" fillId="0" borderId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" applyFont="1" fillId="0" borderId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="3" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="3" applyFill="1" borderId="4" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" applyFont="1" fillId="4" applyFill="1" borderId="5" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" applyFont="1" fillId="4" applyFill="1" borderId="4" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" applyFont="1" fillId="5" applyFill="1" borderId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" applyFont="1" fillId="0" borderId="7" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" applyFont="1" fillId="0" borderId="8" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" applyFont="1" fillId="6" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="7" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" applyFont="1" fillId="8" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="9" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" applyFont="1" fillId="10" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" applyFont="1" fillId="11" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="12" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="13" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" applyFont="1" fillId="14" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" applyFont="1" fillId="15" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="16" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="17" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" applyFont="1" fillId="18" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" applyFont="1" fillId="19" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="20" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="21" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" applyFont="1" fillId="22" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" applyFont="1" fillId="23" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="24" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="25" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" applyFont="1" fillId="26" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" applyFont="1" fillId="27" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="28" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="29" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" applyFont="1" fillId="30" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" applyFont="1" fillId="31" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="32" applyFill="1" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1302,14 +1308,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="33.3636363636364" customWidth="1"/>
     <col min="3" max="3" width="36.3636363636364" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1319,7 +1325,7 @@
       <c r="C1" s="2"/>
       <c r="D1" s="3"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1333,7 +1339,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4">
       <c r="A3" s="2"/>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -1345,7 +1351,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:4">
       <c r="A4" s="2"/>
       <c r="B4" s="2" t="s">
         <v>7</v>
@@ -1357,7 +1363,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:4">
       <c r="A5" s="2"/>
       <c r="B5" s="2" t="s">
         <v>9</v>
@@ -1369,7 +1375,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:4">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
         <v>11</v>
@@ -1381,7 +1387,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:4">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
         <v>13</v>
@@ -1393,7 +1399,7 @@
         <v>0.015</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:4">
       <c r="A8" s="2"/>
       <c r="B8" s="2" t="s">
         <v>15</v>
@@ -1405,7 +1411,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:4">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
         <v>17</v>
@@ -1417,7 +1423,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:4">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
         <v>19</v>
@@ -1429,7 +1435,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:4">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
         <v>21</v>
@@ -1441,7 +1447,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:4">
       <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
         <v>23</v>
@@ -1453,7 +1459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:4">
       <c r="A13" s="2"/>
       <c r="B13" s="2" t="s">
         <v>25</v>
@@ -1465,7 +1471,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:4">
       <c r="A14" s="2"/>
       <c r="B14" s="2" t="s">
         <v>27</v>
@@ -1477,7 +1483,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:4">
       <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
         <v>29</v>
@@ -1489,7 +1495,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:4">
       <c r="A16" s="2"/>
       <c r="B16" s="2" t="s">
         <v>31</v>
@@ -1501,7 +1507,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:4">
       <c r="A17" s="2"/>
       <c r="B17" s="2" t="s">
         <v>33</v>
@@ -1513,7 +1519,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:4">
       <c r="A18" s="2"/>
       <c r="B18" s="2" t="s">
         <v>35</v>
@@ -1525,7 +1531,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:4">
       <c r="A19" s="2"/>
       <c r="B19" s="2" t="s">
         <v>37</v>
@@ -1537,7 +1543,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:4">
       <c r="A20" s="2"/>
       <c r="B20" s="2" t="s">
         <v>39</v>
@@ -1549,41 +1555,41 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="0" t="s">
+    <row r="21" spans="1:4">
+      <c r="B21" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="0" t="s">
+      <c r="C21" t="s">
         <v>42</v>
       </c>
       <c r="D21" s="4">
         <v>50</v>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="0" t="s">
+    <row r="22" spans="1:4">
+      <c r="B22" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="0" t="s">
+      <c r="C22" t="s">
         <v>44</v>
       </c>
       <c r="D22" s="4">
         <v>50</v>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="0" t="s">
+    <row r="23" spans="1:4">
+      <c r="B23" t="s">
         <v>45</v>
       </c>
-      <c r="C23" s="0" t="s">
+      <c r="C23" t="s">
         <v>46</v>
       </c>
       <c r="D23" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="0" t="s">
+    <row r="24" spans="1:4">
+      <c r="B24" t="s">
         <v>47</v>
       </c>
       <c r="C24" s="5" t="s">
@@ -1593,30 +1599,30 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="0" t="s">
+    <row r="25" spans="1:4">
+      <c r="B25" t="s">
         <v>49</v>
       </c>
-      <c r="C25" s="0" t="s">
+      <c r="C25" t="s">
         <v>50</v>
       </c>
       <c r="D25" s="4">
         <v>300</v>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="0" t="s">
+    <row r="26" spans="1:4">
+      <c r="B26" t="s">
         <v>51</v>
       </c>
-      <c r="C26" s="0" t="s">
+      <c r="C26" t="s">
         <v>52</v>
       </c>
       <c r="D26" s="4">
         <v>450</v>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="0" t="s">
+    <row r="27" spans="1:4">
+      <c r="B27" t="s">
         <v>53</v>
       </c>
       <c r="C27" s="5" t="s">
@@ -1626,30 +1632,30 @@
         <v>200</v>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="0" t="s">
+    <row r="28" spans="1:4">
+      <c r="B28" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="0" t="s">
+      <c r="C28" t="s">
         <v>56</v>
       </c>
       <c r="D28" s="4">
         <v>800</v>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="0" t="s">
+    <row r="29" spans="1:4">
+      <c r="B29" t="s">
         <v>57</v>
       </c>
-      <c r="C29" s="0" t="s">
+      <c r="C29" t="s">
         <v>58</v>
       </c>
       <c r="D29" s="4">
         <v>3000</v>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="0" t="s">
+    <row r="30" spans="1:4">
+      <c r="B30" t="s">
         <v>59</v>
       </c>
       <c r="C30" s="5" t="s">
@@ -1659,235 +1665,246 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="0" t="s">
+    <row r="31" spans="1:4">
+      <c r="B31" t="s">
         <v>61</v>
       </c>
-      <c r="C31" s="0" t="s">
+      <c r="C31" t="s">
         <v>62</v>
       </c>
       <c r="D31" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="0" t="s">
+    <row r="32" spans="1:4">
+      <c r="B32" t="s">
         <v>63</v>
       </c>
-      <c r="C32" s="0" t="s">
+      <c r="C32" t="s">
         <v>64</v>
       </c>
       <c r="D32" s="4">
         <v>400</v>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="0" t="s">
+    <row r="33" spans="2:4">
+      <c r="B33" t="s">
         <v>65</v>
       </c>
-      <c r="C33" s="0" t="s">
+      <c r="C33" t="s">
         <v>66</v>
       </c>
       <c r="D33" s="4">
         <v>0.8</v>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="0" t="s">
+    <row r="34" spans="2:4">
+      <c r="B34" t="s">
         <v>67</v>
       </c>
-      <c r="C34" s="0" t="s">
+      <c r="C34" t="s">
         <v>68</v>
       </c>
       <c r="D34" s="4">
         <v>500</v>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="0" t="s">
+    <row r="35" spans="2:4">
+      <c r="B35" t="s">
         <v>69</v>
       </c>
-      <c r="C35" s="0" t="s">
+      <c r="C35" t="s">
         <v>70</v>
       </c>
       <c r="D35" s="4">
         <v>1.2</v>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="0" t="s">
+    <row r="36" spans="2:4">
+      <c r="B36" t="s">
         <v>71</v>
       </c>
-      <c r="C36" s="0" t="s">
+      <c r="C36" t="s">
         <v>72</v>
       </c>
       <c r="D36" s="4">
         <v>0.5</v>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="0" t="s">
+    <row r="37" spans="2:4">
+      <c r="B37" t="s">
         <v>73</v>
       </c>
-      <c r="C37" s="0" t="s">
+      <c r="C37" t="s">
         <v>74</v>
       </c>
       <c r="D37" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="38">
-      <c r="B38" s="0" t="s">
+    <row r="38" spans="2:4">
+      <c r="B38" t="s">
         <v>75</v>
       </c>
-      <c r="C38" s="0" t="s">
+      <c r="C38" t="s">
         <v>76</v>
       </c>
       <c r="D38" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="0" t="s">
+    <row r="39" spans="2:4">
+      <c r="B39" t="s">
         <v>77</v>
       </c>
-      <c r="C39" s="0" t="s">
+      <c r="C39" t="s">
         <v>78</v>
       </c>
       <c r="D39" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="40">
-      <c r="B40" s="0" t="s">
+    <row r="40" spans="2:4">
+      <c r="B40" t="s">
         <v>79</v>
       </c>
-      <c r="C40" s="0" t="s">
+      <c r="C40" t="s">
         <v>80</v>
       </c>
       <c r="D40" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" s="0" t="s">
+    <row r="41" spans="2:4">
+      <c r="B41" t="s">
         <v>81</v>
       </c>
-      <c r="C41" s="0" t="s">
+      <c r="C41" t="s">
         <v>82</v>
       </c>
       <c r="D41" s="4">
         <v>0.01</v>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="0" t="s">
+    <row r="42" spans="2:4">
+      <c r="B42" t="s">
         <v>83</v>
       </c>
-      <c r="C42" s="0" t="s">
+      <c r="C42" t="s">
         <v>84</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="0" t="s">
+    <row r="43" spans="2:4">
+      <c r="B43" t="s">
         <v>86</v>
       </c>
-      <c r="C43" s="0" t="s">
+      <c r="C43" t="s">
         <v>87</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="0" t="s">
+    <row r="44" spans="2:4">
+      <c r="B44" t="s">
         <v>89</v>
       </c>
-      <c r="C44" s="0" t="s">
+      <c r="C44" t="s">
         <v>90</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="0" t="s">
+    <row r="45" spans="2:4">
+      <c r="B45" t="s">
         <v>92</v>
       </c>
-      <c r="C45" s="0" t="s">
+      <c r="C45" t="s">
         <v>93</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" s="0" t="s">
+    <row r="46" spans="2:4">
+      <c r="B46" t="s">
         <v>95</v>
       </c>
-      <c r="C46" s="0" t="s">
+      <c r="C46" t="s">
         <v>96</v>
       </c>
       <c r="D46" s="4">
         <v>300</v>
       </c>
     </row>
-    <row r="47">
-      <c r="B47" s="0" t="s">
+    <row r="47" spans="2:4">
+      <c r="B47" t="s">
         <v>97</v>
       </c>
-      <c r="C47" s="0" t="s">
+      <c r="C47" t="s">
         <v>98</v>
       </c>
       <c r="D47" s="4">
         <v>10000</v>
       </c>
     </row>
-    <row r="48">
-      <c r="B48" s="0" t="s">
+    <row r="48" spans="2:4">
+      <c r="B48" t="s">
         <v>99</v>
       </c>
-      <c r="C48" s="0" t="s">
+      <c r="C48" t="s">
         <v>100</v>
       </c>
       <c r="D48" s="4">
         <v>-5000</v>
       </c>
     </row>
-    <row r="49">
-      <c r="B49" s="0" t="s">
+    <row r="49" spans="2:4">
+      <c r="B49" t="s">
         <v>101</v>
       </c>
-      <c r="C49" s="0" t="s">
+      <c r="C49" t="s">
         <v>102</v>
       </c>
       <c r="D49" s="4">
         <v>50</v>
       </c>
     </row>
-    <row r="50">
-      <c r="B50" s="0" t="s">
+    <row r="50" spans="2:4">
+      <c r="B50" t="s">
         <v>103</v>
       </c>
-      <c r="C50" s="0" t="s">
+      <c r="C50" t="s">
         <v>104</v>
       </c>
       <c r="D50" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="51">
-      <c r="B51" s="0" t="s">
+    <row r="51" spans="2:4">
+      <c r="B51" t="s">
         <v>105</v>
       </c>
-      <c r="C51" s="0" t="s">
+      <c r="C51" t="s">
         <v>106</v>
       </c>
       <c r="D51" s="4">
         <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4">
+      <c r="B52" t="s">
+        <v>107</v>
+      </c>
+      <c r="C52" t="s">
+        <v>108</v>
+      </c>
+      <c r="D52">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -1900,6 +1917,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1911,6 +1929,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -357,10 +357,10 @@
     <t>战斗阶段传送前摇</t>
   </si>
   <si>
-    <t>VisionLossDelay</t>
-  </si>
-  <si>
-    <t>视野消失延迟</t>
+    <t>VisionExpandSpeed</t>
+  </si>
+  <si>
+    <t>视野内缩/外扩速度</t>
   </si>
 </sst>
 </file>
@@ -1904,7 +1904,7 @@
         <v>108</v>
       </c>
       <c r="D52">
-        <v>0.5</v>
+        <v>10000</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="111">
   <si>
     <t>#</t>
   </si>
@@ -361,6 +361,12 @@
   </si>
   <si>
     <t>视野内缩/外扩速度</t>
+  </si>
+  <si>
+    <t>BuildingInteractionRadius</t>
+  </si>
+  <si>
+    <t>建筑面板交互半径（码数）</t>
   </si>
 </sst>
 </file>
@@ -837,148 +843,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1308,7 +1314,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="33.3636363636364" customWidth="1"/>
@@ -1396,7 +1402,7 @@
         <v>14</v>
       </c>
       <c r="D7" s="3">
-        <v>0.015</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1903,9 +1909,41 @@
       <c r="C52" t="s">
         <v>108</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="4">
         <v>10000</v>
       </c>
+    </row>
+    <row r="53" spans="2:4">
+      <c r="B53" t="s">
+        <v>109</v>
+      </c>
+      <c r="C53" t="s">
+        <v>110</v>
+      </c>
+      <c r="D53" s="4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4">
+      <c r="D54" s="4"/>
+    </row>
+    <row r="55" spans="2:4">
+      <c r="D55" s="4"/>
+    </row>
+    <row r="56" spans="2:4">
+      <c r="D56" s="4"/>
+    </row>
+    <row r="57" spans="2:4">
+      <c r="D57" s="4"/>
+    </row>
+    <row r="58" spans="2:4">
+      <c r="D58" s="4"/>
+    </row>
+    <row r="59" spans="2:4">
+      <c r="D59" s="4"/>
+    </row>
+    <row r="60" spans="2:4">
+      <c r="D60" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="127">
   <si>
     <t>#</t>
   </si>
@@ -321,22 +321,58 @@
     <t>28</t>
   </si>
   <si>
-    <t>TauntAdditionalPursuitDistance</t>
-  </si>
-  <si>
-    <t>嘲讽额外追击距离</t>
-  </si>
-  <si>
-    <t>TauntThreatPerLevel</t>
-  </si>
-  <si>
-    <t>嘲讽每级仇恨值</t>
-  </si>
-  <si>
-    <t>BuildingExtraThreat</t>
-  </si>
-  <si>
-    <t>建筑额外仇恨值</t>
+    <t>AggroOuterRange</t>
+  </si>
+  <si>
+    <t>仇恨外圈距离（码数）</t>
+  </si>
+  <si>
+    <t>DamageAlertVisionDuration</t>
+  </si>
+  <si>
+    <t>受击警报临时视野持续秒数</t>
+  </si>
+  <si>
+    <t>DamageAlertVisionRadius</t>
+  </si>
+  <si>
+    <t>受击警报临时视野半径（码数）</t>
+  </si>
+  <si>
+    <t>DamageAlertAllyRadius</t>
+  </si>
+  <si>
+    <t>受击警报友军接收半径（码数）</t>
+  </si>
+  <si>
+    <t>DamageAlertTargetDuration</t>
+  </si>
+  <si>
+    <t>受击警报目标持续秒数</t>
+  </si>
+  <si>
+    <t>MinimumAggroCandidateRange</t>
+  </si>
+  <si>
+    <t>最小仇恨候选距离（码数）</t>
+  </si>
+  <si>
+    <t>DefendPursuitDistance</t>
+  </si>
+  <si>
+    <t>驻守单位最大追击距离（码数）</t>
+  </si>
+  <si>
+    <t>DefendReturnHealthRegenPercentPerSecond</t>
+  </si>
+  <si>
+    <t>驻守单位返航每秒最大生命恢复百分比</t>
+  </si>
+  <si>
+    <t>DefendReturnDamageReductionPercent</t>
+  </si>
+  <si>
+    <t>驻守单位返航减伤百分比</t>
   </si>
   <si>
     <t>DemolishedProdRevenueLossRate</t>
@@ -357,16 +393,28 @@
     <t>战斗阶段传送前摇</t>
   </si>
   <si>
-    <t>VisionExpandSpeed</t>
-  </si>
-  <si>
-    <t>视野内缩/外扩速度</t>
+    <t>VisionFadeSpeed</t>
+  </si>
+  <si>
+    <t>视野透明度渐变速度（每秒Alpha值）</t>
   </si>
   <si>
     <t>BuildingInteractionRadius</t>
   </si>
   <si>
     <t>建筑面板交互半径（码数）</t>
+  </si>
+  <si>
+    <t>DefendReturnMoveSpeedBonus</t>
+  </si>
+  <si>
+    <t>驻守单位返航固定移速加成</t>
+  </si>
+  <si>
+    <t>PlayerOutOfCombatMoveSpeedBonus</t>
+  </si>
+  <si>
+    <t>我方单位脱战固定移速加成</t>
   </si>
 </sst>
 </file>
@@ -1314,7 +1362,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="33.3636363636364" customWidth="1"/>
@@ -1844,7 +1892,7 @@
         <v>96</v>
       </c>
       <c r="D46" s="4">
-        <v>300</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="47" spans="2:4">
@@ -1855,7 +1903,7 @@
         <v>98</v>
       </c>
       <c r="D47" s="4">
-        <v>10000</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="2:4">
@@ -1866,7 +1914,7 @@
         <v>100</v>
       </c>
       <c r="D48" s="4">
-        <v>-5000</v>
+        <v>200</v>
       </c>
     </row>
     <row r="49" spans="2:4">
@@ -1877,7 +1925,7 @@
         <v>102</v>
       </c>
       <c r="D49" s="4">
-        <v>50</v>
+        <v>700</v>
       </c>
     </row>
     <row r="50" spans="2:4">
@@ -1899,7 +1947,7 @@
         <v>106</v>
       </c>
       <c r="D51" s="4">
-        <v>1</v>
+        <v>700</v>
       </c>
     </row>
     <row r="52" spans="2:4">
@@ -1910,7 +1958,7 @@
         <v>108</v>
       </c>
       <c r="D52" s="4">
-        <v>10000</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="53" spans="2:4">
@@ -1921,29 +1969,111 @@
         <v>110</v>
       </c>
       <c r="D53" s="4">
-        <v>90</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54" spans="2:4">
-      <c r="D54" s="4"/>
+      <c r="B54" t="s">
+        <v>111</v>
+      </c>
+      <c r="C54" t="s">
+        <v>112</v>
+      </c>
+      <c r="D54" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="55" spans="2:4">
-      <c r="D55" s="4"/>
+      <c r="B55" t="s">
+        <v>113</v>
+      </c>
+      <c r="C55" t="s">
+        <v>114</v>
+      </c>
+      <c r="D55" s="4">
+        <v>50</v>
+      </c>
     </row>
     <row r="56" spans="2:4">
-      <c r="D56" s="4"/>
+      <c r="B56" t="s">
+        <v>115</v>
+      </c>
+      <c r="C56" t="s">
+        <v>116</v>
+      </c>
+      <c r="D56" s="4">
+        <v>2</v>
+      </c>
     </row>
     <row r="57" spans="2:4">
-      <c r="D57" s="4"/>
+      <c r="B57" t="s">
+        <v>117</v>
+      </c>
+      <c r="C57" t="s">
+        <v>118</v>
+      </c>
+      <c r="D57" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="58" spans="2:4">
-      <c r="D58" s="4"/>
+      <c r="B58" t="s">
+        <v>119</v>
+      </c>
+      <c r="C58" t="s">
+        <v>120</v>
+      </c>
+      <c r="D58" s="4">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="59" spans="2:4">
-      <c r="D59" s="4"/>
+      <c r="B59" t="s">
+        <v>121</v>
+      </c>
+      <c r="C59" t="s">
+        <v>122</v>
+      </c>
+      <c r="D59" s="4">
+        <v>80</v>
+      </c>
     </row>
     <row r="60" spans="2:4">
-      <c r="D60" s="4"/>
+      <c r="B60" t="s">
+        <v>123</v>
+      </c>
+      <c r="C60" t="s">
+        <v>124</v>
+      </c>
+      <c r="D60" s="4">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4">
+      <c r="B61" t="s">
+        <v>125</v>
+      </c>
+      <c r="C61" t="s">
+        <v>126</v>
+      </c>
+      <c r="D61" s="4">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4">
+      <c r="D62" s="4"/>
+    </row>
+    <row r="63" spans="2:4">
+      <c r="D63" s="4"/>
+    </row>
+    <row r="64" spans="2:4">
+      <c r="D64" s="4"/>
+    </row>
+    <row r="65" spans="4:4">
+      <c r="D65" s="4"/>
+    </row>
+    <row r="66" spans="4:4">
+      <c r="D66" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -1570,7 +1570,7 @@
         <v>34</v>
       </c>
       <c r="D17" s="3">
-        <v>1200</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1582,7 +1582,7 @@
         <v>36</v>
       </c>
       <c r="D18" s="3">
-        <v>900</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1594,7 +1594,7 @@
         <v>38</v>
       </c>
       <c r="D19" s="3">
-        <v>900</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="20" spans="1:4">

--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="132">
   <si>
     <t>#</t>
   </si>
@@ -234,13 +234,19 @@
     <t>DefendPhaseEnemyArriveInterval</t>
   </si>
   <si>
-    <t>防御阶段出怪间隔</t>
+    <t>防御阶段全波固定最小出兵间隔（秒）</t>
   </si>
   <si>
     <t>DefendPhaseEnemyMinSpeed</t>
   </si>
   <si>
-    <t>防御阶段出怪移速最小值</t>
+    <t>固定出兵窗口推导用的估算最低移速，不限制关卡内实际移速</t>
+  </si>
+  <si>
+    <t>DefendPhaseEnemyMaxSpeed</t>
+  </si>
+  <si>
+    <t>固定出兵窗口推导用的估算最高移速，不限制关卡内实际移速</t>
   </si>
   <si>
     <t>DefendPhaseEnemyEndlessGrowthRate</t>
@@ -415,6 +421,15 @@
   </si>
   <si>
     <t>我方单位脱战固定移速加成</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>DefendRouteWaypointArrivalRadius</t>
+  </si>
+  <si>
+    <t>防御路线中转传送点抵达半径（码数）</t>
   </si>
 </sst>
 </file>
@@ -888,167 +903,167 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="2" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="3" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="0" applyFont="0" fillId="2" applyFill="1" borderId="1" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="4" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="5" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="6" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="7" applyFont="1" fillId="0" applyFill="0" borderId="2" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="8" applyFont="1" fillId="0" applyFill="0" borderId="2" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="3" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="10" applyFont="1" fillId="3" applyFill="1" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="11" applyFont="1" fillId="4" applyFill="1" borderId="5" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="12" applyFont="1" fillId="4" applyFill="1" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="13" applyFont="1" fillId="5" applyFill="1" borderId="6" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="14" applyFont="1" fillId="0" applyFill="0" borderId="7" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="15" applyFont="1" fillId="0" applyFill="0" borderId="8" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="16" applyFont="1" fillId="6" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="17" applyFont="1" fillId="7" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="18" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1362,14 +1377,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="33.3636363636364" customWidth="1"/>
     <col min="3" max="3" width="36.3636363636364" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1379,7 +1394,7 @@
       <c r="C1" s="2"/>
       <c r="D1" s="3"/>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1393,7 +1408,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3">
       <c r="A3" s="2"/>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -1405,7 +1420,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4">
       <c r="A4" s="2"/>
       <c r="B4" s="2" t="s">
         <v>7</v>
@@ -1417,7 +1432,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5">
       <c r="A5" s="2"/>
       <c r="B5" s="2" t="s">
         <v>9</v>
@@ -1429,7 +1444,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
         <v>11</v>
@@ -1441,7 +1456,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
         <v>13</v>
@@ -1453,7 +1468,7 @@
         <v>0.018</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8">
       <c r="A8" s="2"/>
       <c r="B8" s="2" t="s">
         <v>15</v>
@@ -1465,7 +1480,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
         <v>17</v>
@@ -1477,7 +1492,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
         <v>19</v>
@@ -1489,7 +1504,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
         <v>21</v>
@@ -1501,7 +1516,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12">
       <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
         <v>23</v>
@@ -1513,7 +1528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13">
       <c r="A13" s="2"/>
       <c r="B13" s="2" t="s">
         <v>25</v>
@@ -1525,7 +1540,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14">
       <c r="A14" s="2"/>
       <c r="B14" s="2" t="s">
         <v>27</v>
@@ -1537,7 +1552,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15">
       <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
         <v>29</v>
@@ -1549,7 +1564,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16">
       <c r="A16" s="2"/>
       <c r="B16" s="2" t="s">
         <v>31</v>
@@ -1561,7 +1576,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17">
       <c r="A17" s="2"/>
       <c r="B17" s="2" t="s">
         <v>33</v>
@@ -1573,7 +1588,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18">
       <c r="A18" s="2"/>
       <c r="B18" s="2" t="s">
         <v>35</v>
@@ -1585,7 +1600,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19">
       <c r="A19" s="2"/>
       <c r="B19" s="2" t="s">
         <v>37</v>
@@ -1597,7 +1612,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20">
       <c r="A20" s="2"/>
       <c r="B20" s="2" t="s">
         <v>39</v>
@@ -1609,41 +1624,41 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
-      <c r="B21" t="s">
+    <row r="21">
+      <c r="B21" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="0" t="s">
         <v>42</v>
       </c>
       <c r="D21" s="4">
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
-      <c r="B22" t="s">
+    <row r="22">
+      <c r="B22" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="0" t="s">
         <v>44</v>
       </c>
       <c r="D22" s="4">
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
-      <c r="B23" t="s">
+    <row r="23">
+      <c r="B23" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="0" t="s">
         <v>46</v>
       </c>
       <c r="D23" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
-      <c r="B24" t="s">
+    <row r="24">
+      <c r="B24" s="0" t="s">
         <v>47</v>
       </c>
       <c r="C24" s="5" t="s">
@@ -1653,30 +1668,30 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
-      <c r="B25" t="s">
+    <row r="25">
+      <c r="B25" s="0" t="s">
         <v>49</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="0" t="s">
         <v>50</v>
       </c>
       <c r="D25" s="4">
         <v>300</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
-      <c r="B26" t="s">
+    <row r="26">
+      <c r="B26" s="0" t="s">
         <v>51</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="0" t="s">
         <v>52</v>
       </c>
       <c r="D26" s="4">
         <v>450</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
-      <c r="B27" t="s">
+    <row r="27">
+      <c r="B27" s="0" t="s">
         <v>53</v>
       </c>
       <c r="C27" s="5" t="s">
@@ -1686,30 +1701,30 @@
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
-      <c r="B28" t="s">
+    <row r="28">
+      <c r="B28" s="0" t="s">
         <v>55</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="0" t="s">
         <v>56</v>
       </c>
       <c r="D28" s="4">
         <v>800</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
-      <c r="B29" t="s">
+    <row r="29">
+      <c r="B29" s="0" t="s">
         <v>57</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="0" t="s">
         <v>58</v>
       </c>
       <c r="D29" s="4">
         <v>3000</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
-      <c r="B30" t="s">
+    <row r="30">
+      <c r="B30" s="0" t="s">
         <v>59</v>
       </c>
       <c r="C30" s="5" t="s">
@@ -1719,361 +1734,383 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
-      <c r="B31" t="s">
+    <row r="31">
+      <c r="B31" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="0" t="s">
         <v>62</v>
       </c>
       <c r="D31" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
-      <c r="B32" t="s">
+    <row r="32">
+      <c r="B32" s="0" t="s">
         <v>63</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="0" t="s">
         <v>64</v>
       </c>
       <c r="D32" s="4">
         <v>400</v>
       </c>
     </row>
-    <row r="33" spans="2:4">
-      <c r="B33" t="s">
+    <row r="33">
+      <c r="B33" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="0" t="s">
         <v>66</v>
       </c>
       <c r="D33" s="4">
         <v>0.8</v>
       </c>
     </row>
-    <row r="34" spans="2:4">
-      <c r="B34" t="s">
+    <row r="34">
+      <c r="B34" s="0" t="s">
         <v>67</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="0" t="s">
         <v>68</v>
       </c>
       <c r="D34" s="4">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4">
-      <c r="B35" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="0" t="s">
         <v>69</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="0" t="s">
         <v>70</v>
       </c>
       <c r="D35" s="4">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="D36" s="4">
         <v>1.2</v>
       </c>
     </row>
-    <row r="36" spans="2:4">
-      <c r="B36" t="s">
-        <v>71</v>
-      </c>
-      <c r="C36" t="s">
-        <v>72</v>
-      </c>
-      <c r="D36" s="4">
+    <row r="37">
+      <c r="B37" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="D37" s="4">
         <v>0.5</v>
       </c>
     </row>
-    <row r="37" spans="2:4">
-      <c r="B37" t="s">
-        <v>73</v>
-      </c>
-      <c r="C37" t="s">
-        <v>74</v>
-      </c>
-      <c r="D37" s="4">
+    <row r="38">
+      <c r="B38" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="C38" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="D38" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="2:4">
-      <c r="B38" t="s">
-        <v>75</v>
-      </c>
-      <c r="C38" t="s">
-        <v>76</v>
-      </c>
-      <c r="D38" s="4">
+    <row r="39">
+      <c r="B39" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="C39" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="D39" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="2:4">
-      <c r="B39" t="s">
-        <v>77</v>
-      </c>
-      <c r="C39" t="s">
-        <v>78</v>
-      </c>
-      <c r="D39" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4">
-      <c r="B40" t="s">
+    <row r="40">
+      <c r="B40" s="0" t="s">
         <v>79</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="0" t="s">
         <v>80</v>
       </c>
       <c r="D40" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="2:4">
-      <c r="B41" t="s">
+    <row r="41">
+      <c r="B41" s="0" t="s">
         <v>81</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="0" t="s">
         <v>82</v>
       </c>
       <c r="D41" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="C42" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="D42" s="4">
         <v>0.01</v>
       </c>
     </row>
-    <row r="42" spans="2:4">
-      <c r="B42" t="s">
-        <v>83</v>
-      </c>
-      <c r="C42" t="s">
-        <v>84</v>
-      </c>
-      <c r="D42" s="4" t="s">
+    <row r="43">
+      <c r="B43" s="0" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="43" spans="2:4">
-      <c r="B43" t="s">
+      <c r="C43" s="0" t="s">
         <v>86</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D43" s="4" t="s">
+    </row>
+    <row r="44">
+      <c r="B44" s="0" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="44" spans="2:4">
-      <c r="B44" t="s">
+      <c r="C44" s="0" t="s">
         <v>89</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="D44" s="4" t="s">
+    </row>
+    <row r="45">
+      <c r="B45" s="0" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="45" spans="2:4">
-      <c r="B45" t="s">
+      <c r="C45" s="0" t="s">
         <v>92</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D45" s="4" t="s">
+    </row>
+    <row r="46">
+      <c r="B46" s="0" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="46" spans="2:4">
-      <c r="B46" t="s">
+      <c r="C46" s="0" t="s">
         <v>95</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="D46" s="4">
+    </row>
+    <row r="47">
+      <c r="B47" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="C47" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="D47" s="4">
         <v>1800</v>
       </c>
     </row>
-    <row r="47" spans="2:4">
-      <c r="B47" t="s">
-        <v>97</v>
-      </c>
-      <c r="C47" t="s">
-        <v>98</v>
-      </c>
-      <c r="D47" s="4">
+    <row r="48">
+      <c r="B48" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="C48" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="D48" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="2:4">
-      <c r="B48" t="s">
-        <v>99</v>
-      </c>
-      <c r="C48" t="s">
+    <row r="49">
+      <c r="B49" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="C49" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="D49" s="4">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="C50" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="D50" s="4">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="C51" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="D51" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="C52" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="D52" s="4">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="C53" s="0" t="s">
+        <v>110</v>
+      </c>
+      <c r="D53" s="4">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="C54" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="D54" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="C55" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="D55" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="0" t="s">
+        <v>115</v>
+      </c>
+      <c r="C56" s="0" t="s">
+        <v>116</v>
+      </c>
+      <c r="D56" s="4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="C57" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="D57" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="C58" s="0" t="s">
+        <v>120</v>
+      </c>
+      <c r="D58" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="C59" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="D59" s="4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="C60" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="D60" s="4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="0" t="s">
+        <v>125</v>
+      </c>
+      <c r="C61" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="D61" s="4">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="C62" s="0" t="s">
+        <v>128</v>
+      </c>
+      <c r="D62" s="4">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="B63" s="0" t="s">
+        <v>130</v>
+      </c>
+      <c r="C63" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="D63" s="4">
         <v>100</v>
       </c>
-      <c r="D48" s="4">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="49" spans="2:4">
-      <c r="B49" t="s">
-        <v>101</v>
-      </c>
-      <c r="C49" t="s">
-        <v>102</v>
-      </c>
-      <c r="D49" s="4">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="50" spans="2:4">
-      <c r="B50" t="s">
-        <v>103</v>
-      </c>
-      <c r="C50" t="s">
-        <v>104</v>
-      </c>
-      <c r="D50" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="51" spans="2:4">
-      <c r="B51" t="s">
-        <v>105</v>
-      </c>
-      <c r="C51" t="s">
-        <v>106</v>
-      </c>
-      <c r="D51" s="4">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="52" spans="2:4">
-      <c r="B52" t="s">
-        <v>107</v>
-      </c>
-      <c r="C52" t="s">
-        <v>108</v>
-      </c>
-      <c r="D52" s="4">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="53" spans="2:4">
-      <c r="B53" t="s">
-        <v>109</v>
-      </c>
-      <c r="C53" t="s">
-        <v>110</v>
-      </c>
-      <c r="D53" s="4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="54" spans="2:4">
-      <c r="B54" t="s">
-        <v>111</v>
-      </c>
-      <c r="C54" t="s">
-        <v>112</v>
-      </c>
-      <c r="D54" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="2:4">
-      <c r="B55" t="s">
-        <v>113</v>
-      </c>
-      <c r="C55" t="s">
-        <v>114</v>
-      </c>
-      <c r="D55" s="4">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="56" spans="2:4">
-      <c r="B56" t="s">
-        <v>115</v>
-      </c>
-      <c r="C56" t="s">
-        <v>116</v>
-      </c>
-      <c r="D56" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="57" spans="2:4">
-      <c r="B57" t="s">
-        <v>117</v>
-      </c>
-      <c r="C57" t="s">
-        <v>118</v>
-      </c>
-      <c r="D57" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="2:4">
-      <c r="B58" t="s">
-        <v>119</v>
-      </c>
-      <c r="C58" t="s">
-        <v>120</v>
-      </c>
-      <c r="D58" s="4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="59" spans="2:4">
-      <c r="B59" t="s">
-        <v>121</v>
-      </c>
-      <c r="C59" t="s">
-        <v>122</v>
-      </c>
-      <c r="D59" s="4">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="60" spans="2:4">
-      <c r="B60" t="s">
-        <v>123</v>
-      </c>
-      <c r="C60" t="s">
-        <v>124</v>
-      </c>
-      <c r="D60" s="4">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="61" spans="2:4">
-      <c r="B61" t="s">
-        <v>125</v>
-      </c>
-      <c r="C61" t="s">
-        <v>126</v>
-      </c>
-      <c r="D61" s="4">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="62" spans="2:4">
-      <c r="D62" s="4"/>
-    </row>
-    <row r="63" spans="2:4">
-      <c r="D63" s="4"/>
-    </row>
-    <row r="64" spans="2:4">
+    </row>
+    <row r="64">
       <c r="D64" s="4"/>
     </row>
-    <row r="65" spans="4:4">
+    <row r="65">
       <c r="D65" s="4"/>
     </row>
-    <row r="66" spans="4:4">
+    <row r="66">
       <c r="D66" s="4"/>
+    </row>
+    <row r="67">
+      <c r="D67" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2085,7 +2122,6 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2097,7 +2133,6 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="138">
   <si>
     <t>#</t>
   </si>
@@ -430,6 +430,24 @@
   </si>
   <si>
     <t>防御路线中转传送点抵达半径（码数）</t>
+  </si>
+  <si>
+    <t>WallDetourDistanceThreshold</t>
+  </si>
+  <si>
+    <t>追击目标时允许的绕墙额外距离（码数）</t>
+  </si>
+  <si>
+    <t>SlopeUpperVisionRadius</t>
+  </si>
+  <si>
+    <t>斜坡上单位额外获得高度+1地面视野的半径（码数）</t>
+  </si>
+  <si>
+    <t>BuildingInteractionHoldMinimumDuration</t>
+  </si>
+  <si>
+    <t>建造与升级星星读条最短时间（秒）</t>
   </si>
 </sst>
 </file>
@@ -1377,7 +1395,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D70"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="33.3636363636364" customWidth="1"/>
@@ -2111,6 +2129,39 @@
     </row>
     <row r="67">
       <c r="D67" s="4"/>
+    </row>
+    <row r="68">
+      <c r="B68" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="C68" s="0" t="s">
+        <v>133</v>
+      </c>
+      <c r="D68" s="0">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="C69" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="D69" s="0">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C70" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="D70" s="0">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="160">
   <si>
     <t>#</t>
   </si>
@@ -249,10 +249,13 @@
     <t>固定出兵窗口推导用的估算最高移速，不限制关卡内实际移速</t>
   </si>
   <si>
-    <t>DefendPhaseEnemyEndlessGrowthRate</t>
-  </si>
-  <si>
-    <t>防御阶段无尽出怪增长率</t>
+    <t>EnemyDefenseStrengthGrowthPerExpectedDay</t>
+  </si>
+  <si>
+    <t>防御出怪每个预期天数提供的最终成长倍率增量</t>
+  </si>
+  <si>
+    <t>0.18</t>
   </si>
   <si>
     <t>BaseResourceIncomeDailyGrowth</t>
@@ -432,6 +435,42 @@
     <t>防御路线中转传送点抵达半径（码数）</t>
   </si>
   <si>
+    <t>EnemyGarrisonStrengthGrowthPerExpectedDay</t>
+  </si>
+  <si>
+    <t>据点守军每个预期天数提供的最终成长倍率增量</t>
+  </si>
+  <si>
+    <t>0.10</t>
+  </si>
+  <si>
+    <t>EnemyGarrisonStrengthGrowthHalfWidthRatio</t>
+  </si>
+  <si>
+    <t>据点守军成长曲线半宽占预期天数比例</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>EnemyStrengthEarlyCountPivot</t>
+  </si>
+  <si>
+    <t>少量单位协同增益转为拥堵衰减的数量拐点</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>EnemyStrengthEarlyCountSynergy</t>
+  </si>
+  <si>
+    <t>少量单位数量价值的协同增益强度</t>
+  </si>
+  <si>
+    <t>0.45</t>
+  </si>
+  <si>
     <t>WallDetourDistanceThreshold</t>
   </si>
   <si>
@@ -448,6 +487,33 @@
   </si>
   <si>
     <t>建造与升级星星读条最短时间（秒）</t>
+  </si>
+  <si>
+    <t>EnemyStrengthCrowdingTailScale</t>
+  </si>
+  <si>
+    <t>大量单位拥堵后边际价值衰减尺度</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>EnemyDefenseStrengthGrowthHalfWidthRatio</t>
+  </si>
+  <si>
+    <t>防御出怪成长曲线半宽占预期天数比例</t>
+  </si>
+  <si>
+    <t>EnemyUnitLevel2ValueScale</t>
+  </si>
+  <si>
+    <t>敌方2级单位累计橙髓投入转换为有效战力的折减系数</t>
+  </si>
+  <si>
+    <t>EnemyUnitLevel3ValueScale</t>
+  </si>
+  <si>
+    <t>敌方3级单位累计橙髓投入转换为有效战力的折减系数</t>
   </si>
 </sst>
 </file>
@@ -921,167 +987,167 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="2" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="3" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="0" applyFont="0" fillId="2" applyFill="1" borderId="1" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="4" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="5" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="6" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="7" applyFont="1" fillId="0" applyFill="0" borderId="2" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="8" applyFont="1" fillId="0" applyFill="0" borderId="2" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="3" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="10" applyFont="1" fillId="3" applyFill="1" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="11" applyFont="1" fillId="4" applyFill="1" borderId="5" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="12" applyFont="1" fillId="4" applyFill="1" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="13" applyFont="1" fillId="5" applyFill="1" borderId="6" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="14" applyFont="1" fillId="0" applyFill="0" borderId="7" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="15" applyFont="1" fillId="0" applyFill="0" borderId="8" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="16" applyFont="1" fillId="6" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="17" applyFont="1" fillId="7" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="18" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1395,14 +1461,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D70"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="33.3636363636364" customWidth="1"/>
     <col min="3" max="3" width="36.3636363636364" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1412,7 +1478,7 @@
       <c r="C1" s="2"/>
       <c r="D1" s="3"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1426,7 +1492,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4">
       <c r="A3" s="2"/>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -1438,7 +1504,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:4">
       <c r="A4" s="2"/>
       <c r="B4" s="2" t="s">
         <v>7</v>
@@ -1450,7 +1516,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:4">
       <c r="A5" s="2"/>
       <c r="B5" s="2" t="s">
         <v>9</v>
@@ -1462,7 +1528,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:4">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
         <v>11</v>
@@ -1474,7 +1540,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:4">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
         <v>13</v>
@@ -1486,7 +1552,7 @@
         <v>0.018</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:4">
       <c r="A8" s="2"/>
       <c r="B8" s="2" t="s">
         <v>15</v>
@@ -1498,7 +1564,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:4">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
         <v>17</v>
@@ -1510,7 +1576,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:4">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
         <v>19</v>
@@ -1522,7 +1588,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:4">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
         <v>21</v>
@@ -1534,7 +1600,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:4">
       <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
         <v>23</v>
@@ -1546,7 +1612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:4">
       <c r="A13" s="2"/>
       <c r="B13" s="2" t="s">
         <v>25</v>
@@ -1558,7 +1624,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:4">
       <c r="A14" s="2"/>
       <c r="B14" s="2" t="s">
         <v>27</v>
@@ -1570,7 +1636,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:4">
       <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
         <v>29</v>
@@ -1582,7 +1648,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:4">
       <c r="A16" s="2"/>
       <c r="B16" s="2" t="s">
         <v>31</v>
@@ -1594,7 +1660,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:4">
       <c r="A17" s="2"/>
       <c r="B17" s="2" t="s">
         <v>33</v>
@@ -1606,7 +1672,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:4">
       <c r="A18" s="2"/>
       <c r="B18" s="2" t="s">
         <v>35</v>
@@ -1618,7 +1684,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:4">
       <c r="A19" s="2"/>
       <c r="B19" s="2" t="s">
         <v>37</v>
@@ -1630,7 +1696,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:4">
       <c r="A20" s="2"/>
       <c r="B20" s="2" t="s">
         <v>39</v>
@@ -1642,41 +1708,41 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="0" t="s">
+    <row r="21" spans="1:4">
+      <c r="B21" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="0" t="s">
+      <c r="C21" t="s">
         <v>42</v>
       </c>
       <c r="D21" s="4">
         <v>50</v>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="0" t="s">
+    <row r="22" spans="1:4">
+      <c r="B22" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="0" t="s">
+      <c r="C22" t="s">
         <v>44</v>
       </c>
       <c r="D22" s="4">
         <v>50</v>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="0" t="s">
+    <row r="23" spans="1:4">
+      <c r="B23" t="s">
         <v>45</v>
       </c>
-      <c r="C23" s="0" t="s">
+      <c r="C23" t="s">
         <v>46</v>
       </c>
       <c r="D23" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="0" t="s">
+    <row r="24" spans="1:4">
+      <c r="B24" t="s">
         <v>47</v>
       </c>
       <c r="C24" s="5" t="s">
@@ -1686,30 +1752,30 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="0" t="s">
+    <row r="25" spans="1:4">
+      <c r="B25" t="s">
         <v>49</v>
       </c>
-      <c r="C25" s="0" t="s">
+      <c r="C25" t="s">
         <v>50</v>
       </c>
       <c r="D25" s="4">
         <v>300</v>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="0" t="s">
+    <row r="26" spans="1:4">
+      <c r="B26" t="s">
         <v>51</v>
       </c>
-      <c r="C26" s="0" t="s">
+      <c r="C26" t="s">
         <v>52</v>
       </c>
       <c r="D26" s="4">
         <v>450</v>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="0" t="s">
+    <row r="27" spans="1:4">
+      <c r="B27" t="s">
         <v>53</v>
       </c>
       <c r="C27" s="5" t="s">
@@ -1719,30 +1785,30 @@
         <v>200</v>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="0" t="s">
+    <row r="28" spans="1:4">
+      <c r="B28" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="0" t="s">
+      <c r="C28" t="s">
         <v>56</v>
       </c>
       <c r="D28" s="4">
         <v>800</v>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="0" t="s">
+    <row r="29" spans="1:4">
+      <c r="B29" t="s">
         <v>57</v>
       </c>
-      <c r="C29" s="0" t="s">
+      <c r="C29" t="s">
         <v>58</v>
       </c>
       <c r="D29" s="4">
         <v>3000</v>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="0" t="s">
+    <row r="30" spans="1:4">
+      <c r="B30" t="s">
         <v>59</v>
       </c>
       <c r="C30" s="5" t="s">
@@ -1752,415 +1818,491 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="0" t="s">
+    <row r="31" spans="1:4">
+      <c r="B31" t="s">
         <v>61</v>
       </c>
-      <c r="C31" s="0" t="s">
+      <c r="C31" t="s">
         <v>62</v>
       </c>
       <c r="D31" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="0" t="s">
+    <row r="32" spans="1:4">
+      <c r="B32" t="s">
         <v>63</v>
       </c>
-      <c r="C32" s="0" t="s">
+      <c r="C32" t="s">
         <v>64</v>
       </c>
       <c r="D32" s="4">
         <v>400</v>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="0" t="s">
+    <row r="33" spans="2:4">
+      <c r="B33" t="s">
         <v>65</v>
       </c>
-      <c r="C33" s="0" t="s">
+      <c r="C33" t="s">
         <v>66</v>
       </c>
       <c r="D33" s="4">
         <v>0.8</v>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="0" t="s">
+    <row r="34" spans="2:4">
+      <c r="B34" t="s">
         <v>67</v>
       </c>
-      <c r="C34" s="0" t="s">
+      <c r="C34" t="s">
         <v>68</v>
       </c>
       <c r="D34" s="4">
         <v>300</v>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="0" t="s">
+    <row r="35" spans="2:4">
+      <c r="B35" t="s">
         <v>69</v>
       </c>
-      <c r="C35" s="0" t="s">
+      <c r="C35" t="s">
         <v>70</v>
       </c>
       <c r="D35" s="4">
         <v>1200</v>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="0" t="s">
+    <row r="36" spans="2:4">
+      <c r="B36" t="s">
         <v>71</v>
       </c>
-      <c r="C36" s="0" t="s">
+      <c r="C36" t="s">
         <v>72</v>
       </c>
-      <c r="D36" s="4">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="0" t="s">
+      <c r="D36" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C37" s="0" t="s">
+    </row>
+    <row r="37" spans="2:4">
+      <c r="B37" t="s">
         <v>74</v>
+      </c>
+      <c r="C37" t="s">
+        <v>75</v>
       </c>
       <c r="D37" s="4">
         <v>0.5</v>
       </c>
     </row>
-    <row r="38">
-      <c r="B38" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="C38" s="0" t="s">
+    <row r="38" spans="2:4">
+      <c r="B38" t="s">
         <v>76</v>
+      </c>
+      <c r="C38" t="s">
+        <v>77</v>
       </c>
       <c r="D38" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="0" t="s">
-        <v>77</v>
-      </c>
-      <c r="C39" s="0" t="s">
+    <row r="39" spans="2:4">
+      <c r="B39" t="s">
         <v>78</v>
+      </c>
+      <c r="C39" t="s">
+        <v>79</v>
       </c>
       <c r="D39" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="40">
-      <c r="B40" s="0" t="s">
-        <v>79</v>
-      </c>
-      <c r="C40" s="0" t="s">
+    <row r="40" spans="2:4">
+      <c r="B40" t="s">
         <v>80</v>
+      </c>
+      <c r="C40" t="s">
+        <v>81</v>
       </c>
       <c r="D40" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" s="0" t="s">
-        <v>81</v>
-      </c>
-      <c r="C41" s="0" t="s">
+    <row r="41" spans="2:4">
+      <c r="B41" t="s">
         <v>82</v>
+      </c>
+      <c r="C41" t="s">
+        <v>83</v>
       </c>
       <c r="D41" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="0" t="s">
-        <v>83</v>
-      </c>
-      <c r="C42" s="0" t="s">
+    <row r="42" spans="2:4">
+      <c r="B42" t="s">
         <v>84</v>
+      </c>
+      <c r="C42" t="s">
+        <v>85</v>
       </c>
       <c r="D42" s="4">
         <v>0.01</v>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="0" t="s">
-        <v>85</v>
-      </c>
-      <c r="C43" s="0" t="s">
+    <row r="43" spans="2:4">
+      <c r="B43" t="s">
         <v>86</v>
       </c>
+      <c r="C43" t="s">
+        <v>87</v>
+      </c>
       <c r="D43" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="0" t="s">
         <v>88</v>
       </c>
-      <c r="C44" s="0" t="s">
+    </row>
+    <row r="44" spans="2:4">
+      <c r="B44" t="s">
         <v>89</v>
       </c>
+      <c r="C44" t="s">
+        <v>90</v>
+      </c>
       <c r="D44" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="0" t="s">
         <v>91</v>
       </c>
-      <c r="C45" s="0" t="s">
+    </row>
+    <row r="45" spans="2:4">
+      <c r="B45" t="s">
         <v>92</v>
       </c>
+      <c r="C45" t="s">
+        <v>93</v>
+      </c>
       <c r="D45" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="0" t="s">
         <v>94</v>
       </c>
-      <c r="C46" s="0" t="s">
+    </row>
+    <row r="46" spans="2:4">
+      <c r="B46" t="s">
         <v>95</v>
       </c>
+      <c r="C46" t="s">
+        <v>96</v>
+      </c>
       <c r="D46" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="0" t="s">
         <v>97</v>
       </c>
-      <c r="C47" s="0" t="s">
+    </row>
+    <row r="47" spans="2:4">
+      <c r="B47" t="s">
         <v>98</v>
+      </c>
+      <c r="C47" t="s">
+        <v>99</v>
       </c>
       <c r="D47" s="4">
         <v>1800</v>
       </c>
     </row>
-    <row r="48">
-      <c r="B48" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="C48" s="0" t="s">
+    <row r="48" spans="2:4">
+      <c r="B48" t="s">
         <v>100</v>
+      </c>
+      <c r="C48" t="s">
+        <v>101</v>
       </c>
       <c r="D48" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="49">
-      <c r="B49" s="0" t="s">
-        <v>101</v>
-      </c>
-      <c r="C49" s="0" t="s">
+    <row r="49" spans="1:4">
+      <c r="B49" t="s">
         <v>102</v>
+      </c>
+      <c r="C49" t="s">
+        <v>103</v>
       </c>
       <c r="D49" s="4">
         <v>200</v>
       </c>
     </row>
-    <row r="50">
-      <c r="B50" s="0" t="s">
-        <v>103</v>
-      </c>
-      <c r="C50" s="0" t="s">
+    <row r="50" spans="1:4">
+      <c r="B50" t="s">
         <v>104</v>
+      </c>
+      <c r="C50" t="s">
+        <v>105</v>
       </c>
       <c r="D50" s="4">
         <v>700</v>
       </c>
     </row>
-    <row r="51">
-      <c r="B51" s="0" t="s">
-        <v>105</v>
-      </c>
-      <c r="C51" s="0" t="s">
+    <row r="51" spans="1:4">
+      <c r="B51" t="s">
         <v>106</v>
+      </c>
+      <c r="C51" t="s">
+        <v>107</v>
       </c>
       <c r="D51" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="52">
-      <c r="B52" s="0" t="s">
-        <v>107</v>
-      </c>
-      <c r="C52" s="0" t="s">
+    <row r="52" spans="1:4">
+      <c r="B52" t="s">
         <v>108</v>
+      </c>
+      <c r="C52" t="s">
+        <v>109</v>
       </c>
       <c r="D52" s="4">
         <v>700</v>
       </c>
     </row>
-    <row r="53">
-      <c r="B53" s="0" t="s">
-        <v>109</v>
-      </c>
-      <c r="C53" s="0" t="s">
+    <row r="53" spans="1:4">
+      <c r="B53" t="s">
         <v>110</v>
+      </c>
+      <c r="C53" t="s">
+        <v>111</v>
       </c>
       <c r="D53" s="4">
         <v>1800</v>
       </c>
     </row>
-    <row r="54">
-      <c r="B54" s="0" t="s">
-        <v>111</v>
-      </c>
-      <c r="C54" s="0" t="s">
+    <row r="54" spans="1:4">
+      <c r="B54" t="s">
         <v>112</v>
+      </c>
+      <c r="C54" t="s">
+        <v>113</v>
       </c>
       <c r="D54" s="4">
         <v>20</v>
       </c>
     </row>
-    <row r="55">
-      <c r="B55" s="0" t="s">
-        <v>113</v>
-      </c>
-      <c r="C55" s="0" t="s">
+    <row r="55" spans="1:4">
+      <c r="B55" t="s">
         <v>114</v>
+      </c>
+      <c r="C55" t="s">
+        <v>115</v>
       </c>
       <c r="D55" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="56">
-      <c r="B56" s="0" t="s">
-        <v>115</v>
-      </c>
-      <c r="C56" s="0" t="s">
+    <row r="56" spans="1:4">
+      <c r="B56" t="s">
         <v>116</v>
+      </c>
+      <c r="C56" t="s">
+        <v>117</v>
       </c>
       <c r="D56" s="4">
         <v>50</v>
       </c>
     </row>
-    <row r="57">
-      <c r="B57" s="0" t="s">
-        <v>117</v>
-      </c>
-      <c r="C57" s="0" t="s">
+    <row r="57" spans="1:4">
+      <c r="B57" t="s">
         <v>118</v>
+      </c>
+      <c r="C57" t="s">
+        <v>119</v>
       </c>
       <c r="D57" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="58">
-      <c r="B58" s="0" t="s">
-        <v>119</v>
-      </c>
-      <c r="C58" s="0" t="s">
+    <row r="58" spans="1:4">
+      <c r="B58" t="s">
         <v>120</v>
+      </c>
+      <c r="C58" t="s">
+        <v>121</v>
       </c>
       <c r="D58" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="59">
-      <c r="B59" s="0" t="s">
-        <v>121</v>
-      </c>
-      <c r="C59" s="0" t="s">
+    <row r="59" spans="1:4">
+      <c r="B59" t="s">
         <v>122</v>
+      </c>
+      <c r="C59" t="s">
+        <v>123</v>
       </c>
       <c r="D59" s="4">
         <v>3.5</v>
       </c>
     </row>
-    <row r="60">
-      <c r="B60" s="0" t="s">
-        <v>123</v>
-      </c>
-      <c r="C60" s="0" t="s">
+    <row r="60" spans="1:4">
+      <c r="B60" t="s">
         <v>124</v>
+      </c>
+      <c r="C60" t="s">
+        <v>125</v>
       </c>
       <c r="D60" s="4">
         <v>80</v>
       </c>
     </row>
-    <row r="61">
-      <c r="B61" s="0" t="s">
-        <v>125</v>
-      </c>
-      <c r="C61" s="0" t="s">
+    <row r="61" spans="1:4">
+      <c r="B61" t="s">
         <v>126</v>
+      </c>
+      <c r="C61" t="s">
+        <v>127</v>
       </c>
       <c r="D61" s="4">
         <v>250</v>
       </c>
     </row>
-    <row r="62">
-      <c r="B62" s="0" t="s">
-        <v>127</v>
-      </c>
-      <c r="C62" s="0" t="s">
+    <row r="62" spans="1:4">
+      <c r="B62" t="s">
         <v>128</v>
+      </c>
+      <c r="C62" t="s">
+        <v>129</v>
       </c>
       <c r="D62" s="4">
         <v>500</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="B63" s="0" t="s">
+    <row r="63" spans="1:4">
+      <c r="A63" t="s">
         <v>130</v>
       </c>
-      <c r="C63" s="0" t="s">
+      <c r="B63" t="s">
         <v>131</v>
+      </c>
+      <c r="C63" t="s">
+        <v>132</v>
       </c>
       <c r="D63" s="4">
         <v>100</v>
       </c>
     </row>
-    <row r="64">
-      <c r="D64" s="4"/>
-    </row>
-    <row r="65">
-      <c r="D65" s="4"/>
-    </row>
-    <row r="66">
-      <c r="D66" s="4"/>
-    </row>
-    <row r="67">
-      <c r="D67" s="4"/>
-    </row>
-    <row r="68">
-      <c r="B68" s="0" t="s">
-        <v>132</v>
-      </c>
-      <c r="C68" s="0" t="s">
+    <row r="64" spans="1:4">
+      <c r="B64" t="s">
         <v>133</v>
       </c>
-      <c r="D68" s="0">
+      <c r="C64" t="s">
+        <v>134</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4">
+      <c r="B65" t="s">
+        <v>136</v>
+      </c>
+      <c r="C65" t="s">
+        <v>137</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4">
+      <c r="B66" t="s">
+        <v>139</v>
+      </c>
+      <c r="C66" t="s">
+        <v>140</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4">
+      <c r="B67" t="s">
+        <v>142</v>
+      </c>
+      <c r="C67" t="s">
+        <v>143</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4">
+      <c r="B68" t="s">
+        <v>145</v>
+      </c>
+      <c r="C68" t="s">
+        <v>146</v>
+      </c>
+      <c r="D68">
         <v>500</v>
       </c>
     </row>
-    <row r="69">
-      <c r="B69" s="0" t="s">
-        <v>134</v>
-      </c>
-      <c r="C69" s="0" t="s">
-        <v>135</v>
-      </c>
-      <c r="D69" s="0">
+    <row r="69" spans="2:4">
+      <c r="B69" t="s">
+        <v>147</v>
+      </c>
+      <c r="C69" t="s">
+        <v>148</v>
+      </c>
+      <c r="D69">
         <v>50</v>
       </c>
     </row>
-    <row r="70">
-      <c r="B70" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="C70" s="0" t="s">
-        <v>137</v>
-      </c>
-      <c r="D70" s="0">
-        <v>1</v>
+    <row r="70" spans="2:4">
+      <c r="B70" t="s">
+        <v>149</v>
+      </c>
+      <c r="C70" t="s">
+        <v>150</v>
+      </c>
+      <c r="D70">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4">
+      <c r="B71" t="s">
+        <v>151</v>
+      </c>
+      <c r="C71" t="s">
+        <v>152</v>
+      </c>
+      <c r="D71" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4">
+      <c r="B72" t="s">
+        <v>154</v>
+      </c>
+      <c r="C72" t="s">
+        <v>155</v>
+      </c>
+      <c r="D72" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="73" spans="2:4">
+      <c r="B73" t="s">
+        <v>156</v>
+      </c>
+      <c r="C73" t="s">
+        <v>157</v>
+      </c>
+      <c r="D73">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="74" spans="2:4">
+      <c r="B74" t="s">
+        <v>158</v>
+      </c>
+      <c r="C74" t="s">
+        <v>159</v>
+      </c>
+      <c r="D74">
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -2173,6 +2315,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2184,6 +2327,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="148">
   <si>
     <t>#</t>
   </si>
@@ -66,43 +66,37 @@
     <t>MinMoveSpeed</t>
   </si>
   <si>
-    <t>移速下限</t>
+    <t>移速下限（格/秒）</t>
   </si>
   <si>
     <t>MaxMoveSpeed</t>
   </si>
   <si>
-    <t>移速上限</t>
-  </si>
-  <si>
-    <t>DistanceConversionRate</t>
-  </si>
-  <si>
-    <t>距离码数转换为unity距离的比例</t>
+    <t>移速上限（格/秒）</t>
   </si>
   <si>
     <t>SmallUnitCollisionRadius</t>
   </si>
   <si>
-    <t>轻型单位碰撞半径</t>
+    <t>轻型单位碰撞半径（格）</t>
   </si>
   <si>
     <t>MediumUnitCollisionRadius</t>
   </si>
   <si>
-    <t>中型单位碰撞半径</t>
+    <t>中型单位碰撞半径（格）</t>
   </si>
   <si>
     <t>LargeUnitCollisionRadius</t>
   </si>
   <si>
-    <t>重型单位碰撞半径</t>
+    <t>重型单位碰撞半径（格）</t>
   </si>
   <si>
     <t>SuperLargeUnitCollisionRadius</t>
   </si>
   <si>
-    <t>超重型单位碰撞半径</t>
+    <t>超重型单位碰撞半径（格）</t>
   </si>
   <si>
     <t>DiscardResourceConversionLevel1</t>
@@ -138,19 +132,19 @@
     <t>HeroVisionRadius</t>
   </si>
   <si>
-    <t>英雄视野</t>
+    <t>英雄视野半径（格）</t>
   </si>
   <si>
     <t>UnitVisionRadius</t>
   </si>
   <si>
-    <t>单位视野</t>
+    <t>单位视野半径（格）</t>
   </si>
   <si>
     <t>BuildingVisionRadius</t>
   </si>
   <si>
-    <t>建筑视野</t>
+    <t>建筑视野半径（格）</t>
   </si>
   <si>
     <t>KillRewardSupplyRatio</t>
@@ -180,37 +174,37 @@
     <t>KnockbackForceLevelM1</t>
   </si>
   <si>
-    <t>-1级推力</t>
+    <t>-1级推力（格/秒）</t>
   </si>
   <si>
     <t>KnockbackForceLevel0</t>
   </si>
   <si>
-    <t>0级推力</t>
+    <t>0级推力（格/秒）</t>
   </si>
   <si>
     <t>KnockbackForceLevel1</t>
   </si>
   <si>
-    <t>1级及以上推力</t>
+    <t>1级及以上推力（格/秒）</t>
   </si>
   <si>
     <t>PullForceLevelM1</t>
   </si>
   <si>
-    <t>-1级拉力</t>
+    <t>-1级拉力加速度（格/秒²）</t>
   </si>
   <si>
     <t>PullForceLevel0</t>
   </si>
   <si>
-    <t>0级拉力</t>
+    <t>0级拉力加速度（格/秒²）</t>
   </si>
   <si>
     <t>PullForceLevel1</t>
   </si>
   <si>
-    <t>1级及以上拉力</t>
+    <t>1级及以上拉力加速度（格/秒²）</t>
   </si>
   <si>
     <t>PullDurationLevelM1</t>
@@ -228,34 +222,25 @@
     <t>Friction</t>
   </si>
   <si>
-    <t>摩擦力</t>
-  </si>
-  <si>
-    <t>DefendPhaseEnemyArriveInterval</t>
-  </si>
-  <si>
-    <t>防御阶段全波固定最小出兵间隔（秒）</t>
+    <t>摩擦减速度（格/秒²）</t>
+  </si>
+  <si>
+    <t>DefendPhaseSameGroupSpawnIntervalSeconds</t>
+  </si>
+  <si>
+    <t>同一防御小队相邻敌人的固定出兵间隔（秒）</t>
   </si>
   <si>
     <t>DefendPhaseEnemyMinSpeed</t>
   </si>
   <si>
-    <t>固定出兵窗口推导用的估算最低移速，不限制关卡内实际移速</t>
+    <t>固定出兵窗口推导用的估算最低移速（格/秒），不限制关卡内实际移速</t>
   </si>
   <si>
     <t>DefendPhaseEnemyMaxSpeed</t>
   </si>
   <si>
-    <t>固定出兵窗口推导用的估算最高移速，不限制关卡内实际移速</t>
-  </si>
-  <si>
-    <t>EnemyDefenseStrengthGrowthPerExpectedDay</t>
-  </si>
-  <si>
-    <t>防御出怪每个预期天数提供的最终成长倍率增量</t>
-  </si>
-  <si>
-    <t>0.18</t>
+    <t>固定出兵窗口推导用的估算最高移速（格/秒），不限制关卡内实际移速</t>
   </si>
   <si>
     <t>BaseResourceIncomeDailyGrowth</t>
@@ -300,40 +285,28 @@
     <t>关卡偏移率铜角标阈值</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>OffsetBadgeSilverThreshold</t>
   </si>
   <si>
     <t>关卡偏移率银角标阈值</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
     <t>OffsetBadgeGoldThreshold</t>
   </si>
   <si>
     <t>关卡偏移率金角标阈值</t>
   </si>
   <si>
-    <t>24</t>
-  </si>
-  <si>
     <t>OffsetBadgeDiamondThreshold</t>
   </si>
   <si>
     <t>关卡偏移率钻角标阈值</t>
   </si>
   <si>
-    <t>28</t>
-  </si>
-  <si>
     <t>AggroOuterRange</t>
   </si>
   <si>
-    <t>仇恨外圈距离（码数）</t>
+    <t>仇恨外圈距离（格）</t>
   </si>
   <si>
     <t>DamageAlertVisionDuration</t>
@@ -345,13 +318,13 @@
     <t>DamageAlertVisionRadius</t>
   </si>
   <si>
-    <t>受击警报临时视野半径（码数）</t>
+    <t>受击警报临时视野半径（格）</t>
   </si>
   <si>
     <t>DamageAlertAllyRadius</t>
   </si>
   <si>
-    <t>受击警报友军接收半径（码数）</t>
+    <t>受击警报友军接收半径（格）</t>
   </si>
   <si>
     <t>DamageAlertTargetDuration</t>
@@ -363,13 +336,13 @@
     <t>MinimumAggroCandidateRange</t>
   </si>
   <si>
-    <t>最小仇恨候选距离（码数）</t>
+    <t>最小仇恨候选距离（格）</t>
   </si>
   <si>
     <t>DefendPursuitDistance</t>
   </si>
   <si>
-    <t>驻守单位最大追击距离（码数）</t>
+    <t>驻守单位最大追击距离（格）</t>
   </si>
   <si>
     <t>DefendReturnHealthRegenPercentPerSecond</t>
@@ -411,19 +384,19 @@
     <t>BuildingInteractionRadius</t>
   </si>
   <si>
-    <t>建筑面板交互半径（码数）</t>
+    <t>建筑面板交互半径（格）</t>
   </si>
   <si>
     <t>DefendReturnMoveSpeedBonus</t>
   </si>
   <si>
-    <t>驻守单位返航固定移速加成</t>
+    <t>驻守单位返航固定移速加成（格/秒）</t>
   </si>
   <si>
     <t>PlayerOutOfCombatMoveSpeedBonus</t>
   </si>
   <si>
-    <t>我方单位脱战固定移速加成</t>
+    <t>我方单位脱战固定移速加成（格/秒）</t>
   </si>
   <si>
     <t/>
@@ -432,55 +405,19 @@
     <t>DefendRouteWaypointArrivalRadius</t>
   </si>
   <si>
-    <t>防御路线中转传送点抵达半径（码数）</t>
-  </si>
-  <si>
-    <t>EnemyGarrisonStrengthGrowthPerExpectedDay</t>
-  </si>
-  <si>
-    <t>据点守军每个预期天数提供的最终成长倍率增量</t>
-  </si>
-  <si>
-    <t>0.10</t>
-  </si>
-  <si>
-    <t>EnemyGarrisonStrengthGrowthHalfWidthRatio</t>
-  </si>
-  <si>
-    <t>据点守军成长曲线半宽占预期天数比例</t>
-  </si>
-  <si>
-    <t>0.25</t>
-  </si>
-  <si>
-    <t>EnemyStrengthEarlyCountPivot</t>
-  </si>
-  <si>
-    <t>少量单位协同增益转为拥堵衰减的数量拐点</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>EnemyStrengthEarlyCountSynergy</t>
-  </si>
-  <si>
-    <t>少量单位数量价值的协同增益强度</t>
-  </si>
-  <si>
-    <t>0.45</t>
+    <t>防御路线中转传送点抵达半径（格）</t>
   </si>
   <si>
     <t>WallDetourDistanceThreshold</t>
   </si>
   <si>
-    <t>追击目标时允许的绕墙额外距离（码数）</t>
+    <t>追击目标时允许的绕墙额外距离（格）</t>
   </si>
   <si>
     <t>SlopeUpperVisionRadius</t>
   </si>
   <si>
-    <t>斜坡上单位额外获得高度+1地面视野的半径（码数）</t>
+    <t>斜坡上单位额外获得高度+1地面视野的半径（格）</t>
   </si>
   <si>
     <t>BuildingInteractionHoldMinimumDuration</t>
@@ -489,31 +426,58 @@
     <t>建造与升级星星读条最短时间（秒）</t>
   </si>
   <si>
-    <t>EnemyStrengthCrowdingTailScale</t>
-  </si>
-  <si>
-    <t>大量单位拥堵后边际价值衰减尺度</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>EnemyDefenseStrengthGrowthHalfWidthRatio</t>
-  </si>
-  <si>
-    <t>防御出怪成长曲线半宽占预期天数比例</t>
-  </si>
-  <si>
-    <t>EnemyUnitLevel2ValueScale</t>
-  </si>
-  <si>
-    <t>敌方2级单位累计橙髓投入转换为有效战力的折减系数</t>
-  </si>
-  <si>
-    <t>EnemyUnitLevel3ValueScale</t>
-  </si>
-  <si>
-    <t>敌方3级单位累计橙髓投入转换为有效战力的折减系数</t>
+    <t>EnemyUnitLevel2ResourceEquivalentScale</t>
+  </si>
+  <si>
+    <t>敌方2级单位累计资源投入转换为单兵资源等价量的折减系数</t>
+  </si>
+  <si>
+    <t>EnemyUnitLevel3ResourceEquivalentScale</t>
+  </si>
+  <si>
+    <t>敌方3级单位累计资源投入转换为单兵资源等价量的折减系数</t>
+  </si>
+  <si>
+    <t>EnemyGarrisonDay2IncrementPerDay1BaseResourceEquivalent</t>
+  </si>
+  <si>
+    <t>守军Day2新增资源等价量占Day1初始资源等价量的比例</t>
+  </si>
+  <si>
+    <t>EnemyGarrisonPreExpectedDailyIncrementIncreasePerDay1BaseResourceEquivalent</t>
+  </si>
+  <si>
+    <t>守军预期日前每日新增量固定再增加的Day1初始资源等价量比例；第d日增量=Day2增量+本值*(d-2)</t>
+  </si>
+  <si>
+    <t>EnemyGarrisonPostExpectedDailyIncrementMultiplier</t>
+  </si>
+  <si>
+    <t>守军预期日后下一日增量乘以前一日增量的倍率</t>
+  </si>
+  <si>
+    <t>EnemyDefenseDay2IncrementPerDay1BaseResourceEquivalent</t>
+  </si>
+  <si>
+    <t>防御出怪Day2新增资源等价量占Day1初始资源等价量的比例</t>
+  </si>
+  <si>
+    <t>EnemyDefensePreExpectedDailyIncrementIncreasePerDay1BaseResourceEquivalent</t>
+  </si>
+  <si>
+    <t>出怪预期日前每日新增量固定再增加的Day1初始资源等价量比例；第d日增量=Day2增量+本值*(d-2)</t>
+  </si>
+  <si>
+    <t>EnemyDefensePostExpectedDailyIncrementMultiplier</t>
+  </si>
+  <si>
+    <t>防御出怪预期日后下一日增量乘以前一日增量的倍率</t>
+  </si>
+  <si>
+    <t>EnemySquadResourceEquivalentMaximumResolvedUnitCount</t>
+  </si>
+  <si>
+    <t>单个敌方小队允许求解的最大单位数，仅作明确数据上限</t>
   </si>
 </sst>
 </file>
@@ -1135,7 +1099,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1145,6 +1109,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
@@ -1461,7 +1428,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="33.3636363636364" customWidth="1"/>
@@ -1500,7 +1467,7 @@
       <c r="C3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="4">
         <v>10</v>
       </c>
     </row>
@@ -1512,7 +1479,7 @@
       <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="4">
         <v>700</v>
       </c>
     </row>
@@ -1524,8 +1491,8 @@
       <c r="C5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="3">
-        <v>100</v>
+      <c r="D5" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1536,8 +1503,8 @@
       <c r="C6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="3">
-        <v>1000</v>
+      <c r="D6" s="4">
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1548,8 +1515,8 @@
       <c r="C7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="3">
-        <v>0.018</v>
+      <c r="D7" s="4">
+        <v>0.2</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1560,8 +1527,8 @@
       <c r="C8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="3">
-        <v>12</v>
+      <c r="D8" s="4">
+        <v>0.4</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1572,8 +1539,8 @@
       <c r="C9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="3">
-        <v>22</v>
+      <c r="D9" s="4">
+        <v>0.6</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1584,8 +1551,8 @@
       <c r="C10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="3">
-        <v>36</v>
+      <c r="D10" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1596,8 +1563,8 @@
       <c r="C11" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="3">
-        <v>54</v>
+      <c r="D11" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1608,8 +1575,8 @@
       <c r="C12" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="3">
-        <v>1</v>
+      <c r="D12" s="4">
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1620,8 +1587,8 @@
       <c r="C13" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="3">
-        <v>2</v>
+      <c r="D13" s="4">
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1632,8 +1599,8 @@
       <c r="C14" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="3">
-        <v>3</v>
+      <c r="D14" s="4">
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1644,7 +1611,7 @@
       <c r="C15" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="4">
         <v>10</v>
       </c>
     </row>
@@ -1656,8 +1623,8 @@
       <c r="C16" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="3">
-        <v>10</v>
+      <c r="D16" s="4">
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1668,8 +1635,8 @@
       <c r="C17" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="3">
-        <v>1500</v>
+      <c r="D17" s="4">
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1680,8 +1647,8 @@
       <c r="C18" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="3">
-        <v>1200</v>
+      <c r="D18" s="4">
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1692,20 +1659,19 @@
       <c r="C19" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D19" s="3">
-        <v>1200</v>
+      <c r="D19" s="4">
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2" t="s">
+      <c r="B20" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" t="s">
         <v>40</v>
       </c>
-      <c r="D20" s="3">
-        <v>10</v>
+      <c r="D20" s="4">
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1727,29 +1693,29 @@
         <v>44</v>
       </c>
       <c r="D22" s="4">
-        <v>50</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="B23" t="s">
         <v>45</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="6" t="s">
         <v>46</v>
       </c>
       <c r="D23" s="4">
-        <v>1</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="B24" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" t="s">
         <v>48</v>
       </c>
       <c r="D24" s="4">
-        <v>100</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1760,29 +1726,29 @@
         <v>50</v>
       </c>
       <c r="D25" s="4">
-        <v>300</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="B26" t="s">
         <v>51</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="6" t="s">
         <v>52</v>
       </c>
       <c r="D26" s="4">
-        <v>450</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="B27" t="s">
         <v>53</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" t="s">
         <v>54</v>
       </c>
       <c r="D27" s="4">
-        <v>200</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1793,29 +1759,29 @@
         <v>56</v>
       </c>
       <c r="D28" s="4">
-        <v>800</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="B29" t="s">
         <v>57</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="6" t="s">
         <v>58</v>
       </c>
       <c r="D29" s="4">
-        <v>3000</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="B30" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" t="s">
         <v>60</v>
       </c>
       <c r="D30" s="4">
-        <v>0.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1826,7 +1792,7 @@
         <v>62</v>
       </c>
       <c r="D31" s="4">
-        <v>1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1837,7 +1803,7 @@
         <v>64</v>
       </c>
       <c r="D32" s="4">
-        <v>400</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:4">
@@ -1848,7 +1814,7 @@
         <v>66</v>
       </c>
       <c r="D33" s="4">
-        <v>0.8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="2:4">
@@ -1859,7 +1825,7 @@
         <v>68</v>
       </c>
       <c r="D34" s="4">
-        <v>300</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="2:4">
@@ -1870,7 +1836,7 @@
         <v>70</v>
       </c>
       <c r="D35" s="4">
-        <v>1200</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="36" spans="2:4">
@@ -1880,27 +1846,27 @@
       <c r="C36" t="s">
         <v>72</v>
       </c>
-      <c r="D36" s="4" t="s">
-        <v>73</v>
+      <c r="D36" s="4">
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" t="s">
         <v>74</v>
       </c>
-      <c r="C37" t="s">
-        <v>75</v>
-      </c>
       <c r="D37" s="4">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" t="s">
+        <v>75</v>
+      </c>
+      <c r="C38" t="s">
         <v>76</v>
-      </c>
-      <c r="C38" t="s">
-        <v>77</v>
       </c>
       <c r="D38" s="4">
         <v>3</v>
@@ -1908,401 +1874,390 @@
     </row>
     <row r="39" spans="2:4">
       <c r="B39" t="s">
+        <v>77</v>
+      </c>
+      <c r="C39" t="s">
         <v>78</v>
       </c>
-      <c r="C39" t="s">
-        <v>79</v>
-      </c>
       <c r="D39" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" t="s">
+        <v>79</v>
+      </c>
+      <c r="C40" t="s">
         <v>80</v>
       </c>
-      <c r="C40" t="s">
-        <v>81</v>
-      </c>
       <c r="D40" s="4">
-        <v>3</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" t="s">
+        <v>81</v>
+      </c>
+      <c r="C41" t="s">
         <v>82</v>
       </c>
-      <c r="C41" t="s">
-        <v>83</v>
-      </c>
-      <c r="D41" s="4">
-        <v>3</v>
+      <c r="D41" s="5">
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" t="s">
+        <v>83</v>
+      </c>
+      <c r="C42" t="s">
         <v>84</v>
       </c>
-      <c r="C42" t="s">
-        <v>85</v>
-      </c>
-      <c r="D42" s="4">
-        <v>0.01</v>
+      <c r="D42" s="5">
+        <v>18</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" t="s">
+        <v>85</v>
+      </c>
+      <c r="C43" t="s">
         <v>86</v>
       </c>
-      <c r="C43" t="s">
-        <v>87</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>88</v>
+      <c r="D43" s="5">
+        <v>24</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C44" t="s">
-        <v>90</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
+      </c>
+      <c r="D44" s="5">
+        <v>28</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C45" t="s">
-        <v>93</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
+      </c>
+      <c r="D45" s="4">
+        <v>32</v>
       </c>
     </row>
     <row r="46" spans="2:4">
       <c r="B46" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C46" t="s">
-        <v>96</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>97</v>
+        <v>92</v>
+      </c>
+      <c r="D46" s="4">
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="2:4">
       <c r="B47" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C47" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D47" s="4">
-        <v>1800</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="2:4">
       <c r="B48" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C48" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D48" s="4">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="B49" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C49" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D49" s="4">
-        <v>200</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="B50" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C50" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D50" s="4">
-        <v>700</v>
+        <v>12</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="B51" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C51" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D51" s="4">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="B52" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C52" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D52" s="4">
-        <v>700</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="B53" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C53" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D53" s="4">
-        <v>1800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="B54" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C54" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D54" s="4">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="B55" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C55" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D55" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="B56" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C56" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D56" s="4">
-        <v>50</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="B57" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C57" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D57" s="4">
-        <v>2</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="B58" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C58" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D58" s="4">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="B59" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C59" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D59" s="4">
-        <v>3.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="B60" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C60" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D60" s="4">
-        <v>80</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:4">
+      <c r="A61" t="s">
+        <v>121</v>
+      </c>
       <c r="B61" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C61" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D61" s="4">
-        <v>250</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="B62" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C62" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D62" s="4">
-        <v>500</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63" spans="1:4">
-      <c r="A63" t="s">
-        <v>130</v>
-      </c>
       <c r="B63" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C63" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D63" s="4">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="B64" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C64" t="s">
-        <v>134</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>135</v>
+        <v>129</v>
+      </c>
+      <c r="D64" s="4">
+        <v>0.4</v>
       </c>
     </row>
     <row r="65" spans="2:4">
       <c r="B65" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C65" t="s">
-        <v>137</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>138</v>
+        <v>131</v>
+      </c>
+      <c r="D65" s="4">
+        <v>0.8</v>
       </c>
     </row>
     <row r="66" spans="2:4">
       <c r="B66" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="C66" t="s">
-        <v>140</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>141</v>
+        <v>133</v>
+      </c>
+      <c r="D66" s="4">
+        <v>0.7</v>
       </c>
     </row>
     <row r="67" spans="2:4">
       <c r="B67" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="C67" t="s">
-        <v>143</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>144</v>
+        <v>135</v>
+      </c>
+      <c r="D67" s="5">
+        <v>0.2</v>
       </c>
     </row>
     <row r="68" spans="2:4">
       <c r="B68" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="C68" t="s">
-        <v>146</v>
-      </c>
-      <c r="D68">
-        <v>500</v>
+        <v>137</v>
+      </c>
+      <c r="D68" s="5">
+        <v>0.2</v>
       </c>
     </row>
     <row r="69" spans="2:4">
       <c r="B69" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C69" t="s">
-        <v>148</v>
-      </c>
-      <c r="D69">
-        <v>50</v>
+        <v>139</v>
+      </c>
+      <c r="D69" s="5">
+        <v>0.6</v>
       </c>
     </row>
     <row r="70" spans="2:4">
       <c r="B70" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="C70" t="s">
-        <v>150</v>
-      </c>
-      <c r="D70">
-        <v>0.4</v>
+        <v>141</v>
+      </c>
+      <c r="D70" s="5">
+        <v>0.6</v>
       </c>
     </row>
     <row r="71" spans="2:4">
       <c r="B71" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="C71" t="s">
-        <v>152</v>
-      </c>
-      <c r="D71" t="s">
-        <v>153</v>
+        <v>143</v>
+      </c>
+      <c r="D71" s="5">
+        <v>0.6</v>
       </c>
     </row>
     <row r="72" spans="2:4">
       <c r="B72" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="C72" t="s">
-        <v>155</v>
-      </c>
-      <c r="D72" t="s">
-        <v>138</v>
+        <v>145</v>
+      </c>
+      <c r="D72" s="5">
+        <v>0.7</v>
       </c>
     </row>
     <row r="73" spans="2:4">
       <c r="B73" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="C73" t="s">
-        <v>157</v>
-      </c>
-      <c r="D73">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="74" spans="2:4">
-      <c r="B74" t="s">
-        <v>158</v>
-      </c>
-      <c r="C74" t="s">
-        <v>159</v>
-      </c>
-      <c r="D74">
-        <v>0.7</v>
+        <v>147</v>
+      </c>
+      <c r="D73" s="4">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -1624,7 +1624,7 @@
         <v>32</v>
       </c>
       <c r="D16" s="4">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1636,7 +1636,7 @@
         <v>34</v>
       </c>
       <c r="D17" s="4">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1648,7 +1648,7 @@
         <v>36</v>
       </c>
       <c r="D18" s="4">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:4">

--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\Avenge\AAAGameData\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FED689E-D8FA-4C06-8E75-B42D83E7CD13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="10480"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,12 +30,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="150">
   <si>
     <t>#</t>
   </si>
@@ -478,19 +482,19 @@
   </si>
   <si>
     <t>单个敌方小队允许求解的最大单位数，仅作明确数据上限</t>
+  </si>
+  <si>
+    <t>EnemyStrongholdFriendlyUnitDeployRadius</t>
+  </si>
+  <si>
+    <t>敌方据点内允许部署卡牌的我方单位接应半径（格）</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -505,345 +509,21 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -851,255 +531,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1114,65 +552,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1422,20 +816,20 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D73"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D74"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="33.3636363636364" customWidth="1"/>
-    <col min="3" max="3" width="36.3636363636364" customWidth="1"/>
+    <col min="2" max="2" width="33.36328125" customWidth="1"/>
+    <col min="3" max="3" width="36.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1445,7 +839,7 @@
       <c r="C1" s="2"/>
       <c r="D1" s="3"/>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1459,7 +853,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -1471,7 +865,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="2" t="s">
         <v>7</v>
@@ -1483,7 +877,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2" t="s">
         <v>9</v>
@@ -1495,7 +889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
         <v>11</v>
@@ -1507,7 +901,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
         <v>13</v>
@@ -1519,7 +913,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2" t="s">
         <v>15</v>
@@ -1531,7 +925,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
         <v>17</v>
@@ -1543,7 +937,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
         <v>19</v>
@@ -1555,7 +949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
         <v>21</v>
@@ -1567,7 +961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
         <v>23</v>
@@ -1579,7 +973,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2" t="s">
         <v>25</v>
@@ -1591,7 +985,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2" t="s">
         <v>27</v>
@@ -1603,7 +997,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
         <v>29</v>
@@ -1615,7 +1009,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2" t="s">
         <v>31</v>
@@ -1627,7 +1021,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2" t="s">
         <v>33</v>
@@ -1639,7 +1033,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2" t="s">
         <v>35</v>
@@ -1651,642 +1045,652 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D19" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D20" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
-      <c r="B20" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
         <v>39</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C21" t="s">
         <v>40</v>
-      </c>
-      <c r="D20" s="4">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="B21" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" t="s">
-        <v>42</v>
       </c>
       <c r="D21" s="4">
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" s="4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
         <v>43</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C23" t="s">
         <v>44</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D23" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
-      <c r="B23" t="s">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
         <v>45</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C24" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D24" s="4">
         <v>1.8</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
-      <c r="B24" t="s">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
         <v>47</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C25" t="s">
         <v>48</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D25" s="4">
         <v>5.4</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
-      <c r="B25" t="s">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
         <v>49</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C26" t="s">
         <v>50</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D26" s="4">
         <v>8.1</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
-      <c r="B26" t="s">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
         <v>51</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C27" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D27" s="4">
         <v>3.6</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
-      <c r="B27" t="s">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
         <v>53</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C28" t="s">
         <v>54</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D28" s="4">
         <v>14.4</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
-      <c r="B28" t="s">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
         <v>55</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C29" t="s">
         <v>56</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D29" s="4">
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
-      <c r="B29" t="s">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
         <v>57</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C30" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D30" s="4">
         <v>0.4</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
-      <c r="B30" t="s">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
         <v>59</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C31" t="s">
         <v>60</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D31" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
-      <c r="B31" t="s">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
         <v>61</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C32" t="s">
         <v>62</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D32" s="4">
         <v>7.2</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
-      <c r="B32" t="s">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
         <v>63</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C33" t="s">
         <v>64</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D33" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="2:4">
-      <c r="B33" t="s">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
         <v>65</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C34" t="s">
         <v>66</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D34" s="4">
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="2:4">
-      <c r="B34" t="s">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
         <v>67</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C35" t="s">
         <v>68</v>
       </c>
-      <c r="D34" s="4">
+      <c r="D35" s="4">
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="2:4">
-      <c r="B35" t="s">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
         <v>69</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C36" t="s">
         <v>70</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D36" s="4">
         <v>0.5</v>
       </c>
     </row>
-    <row r="36" spans="2:4">
-      <c r="B36" t="s">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
         <v>71</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C37" t="s">
         <v>72</v>
       </c>
-      <c r="D36" s="4">
+      <c r="D37" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:4">
-      <c r="B37" t="s">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
         <v>73</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C38" t="s">
         <v>74</v>
       </c>
-      <c r="D37" s="4">
+      <c r="D38" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="2:4">
-      <c r="B38" t="s">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
         <v>75</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C39" t="s">
         <v>76</v>
-      </c>
-      <c r="D38" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:4">
-      <c r="B39" t="s">
-        <v>77</v>
-      </c>
-      <c r="C39" t="s">
-        <v>78</v>
       </c>
       <c r="D39" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="2:4">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
+        <v>77</v>
+      </c>
+      <c r="C40" t="s">
+        <v>78</v>
+      </c>
+      <c r="D40" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
         <v>79</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C41" t="s">
         <v>80</v>
       </c>
-      <c r="D40" s="4">
+      <c r="D41" s="4">
         <v>0.01</v>
       </c>
     </row>
-    <row r="41" spans="2:4">
-      <c r="B41" t="s">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
         <v>81</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C42" t="s">
         <v>82</v>
       </c>
-      <c r="D41" s="5">
+      <c r="D42" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="2:4">
-      <c r="B42" t="s">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
         <v>83</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C43" t="s">
         <v>84</v>
       </c>
-      <c r="D42" s="5">
+      <c r="D43" s="5">
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="2:4">
-      <c r="B43" t="s">
+    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
         <v>85</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C44" t="s">
         <v>86</v>
       </c>
-      <c r="D43" s="5">
+      <c r="D44" s="5">
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="2:4">
-      <c r="B44" t="s">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
         <v>87</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C45" t="s">
         <v>88</v>
       </c>
-      <c r="D44" s="5">
+      <c r="D45" s="5">
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="2:4">
-      <c r="B45" t="s">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
         <v>89</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C46" t="s">
         <v>90</v>
       </c>
-      <c r="D45" s="4">
+      <c r="D46" s="4">
         <v>32</v>
       </c>
     </row>
-    <row r="46" spans="2:4">
-      <c r="B46" t="s">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
         <v>91</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C47" t="s">
         <v>92</v>
       </c>
-      <c r="D46" s="4">
+      <c r="D47" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="2:4">
-      <c r="B47" t="s">
+    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
         <v>93</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C48" t="s">
         <v>94</v>
       </c>
-      <c r="D47" s="4">
+      <c r="D48" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="2:4">
-      <c r="B48" t="s">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
         <v>95</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C49" t="s">
         <v>96</v>
       </c>
-      <c r="D48" s="4">
+      <c r="D49" s="4">
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
-      <c r="B49" t="s">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
         <v>97</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C50" t="s">
         <v>98</v>
       </c>
-      <c r="D49" s="4">
+      <c r="D50" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
-      <c r="B50" t="s">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
         <v>99</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C51" t="s">
         <v>100</v>
       </c>
-      <c r="D50" s="4">
+      <c r="D51" s="4">
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
-      <c r="B51" t="s">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
         <v>101</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C52" t="s">
         <v>102</v>
       </c>
-      <c r="D51" s="4">
+      <c r="D52" s="4">
         <v>32</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
-      <c r="B52" t="s">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
         <v>103</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C53" t="s">
         <v>104</v>
       </c>
-      <c r="D52" s="4">
+      <c r="D53" s="4">
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
-      <c r="B53" t="s">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
         <v>105</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C54" t="s">
         <v>106</v>
       </c>
-      <c r="D53" s="4">
+      <c r="D54" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
-      <c r="B54" t="s">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
         <v>107</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C55" t="s">
         <v>108</v>
       </c>
-      <c r="D54" s="4">
+      <c r="D55" s="4">
         <v>50</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
-      <c r="B55" t="s">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
         <v>109</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C56" t="s">
         <v>110</v>
       </c>
-      <c r="D55" s="4">
+      <c r="D56" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
-      <c r="B56" t="s">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
         <v>111</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C57" t="s">
         <v>112</v>
       </c>
-      <c r="D56" s="4">
+      <c r="D57" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
-      <c r="B57" t="s">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B58" t="s">
         <v>113</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C58" t="s">
         <v>114</v>
       </c>
-      <c r="D57" s="4">
+      <c r="D58" s="4">
         <v>3.5</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
-      <c r="B58" t="s">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
         <v>115</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C59" t="s">
         <v>116</v>
       </c>
-      <c r="D58" s="4">
+      <c r="D59" s="4">
         <v>1.2</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
-      <c r="B59" t="s">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B60" t="s">
         <v>117</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C60" t="s">
         <v>118</v>
       </c>
-      <c r="D59" s="4">
+      <c r="D60" s="4">
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
-      <c r="B60" t="s">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B61" t="s">
         <v>119</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C61" t="s">
         <v>120</v>
       </c>
-      <c r="D60" s="4">
+      <c r="D61" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
-      <c r="A61" t="s">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
         <v>121</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B62" t="s">
         <v>122</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C62" t="s">
         <v>123</v>
       </c>
-      <c r="D61" s="4">
+      <c r="D62" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:4">
-      <c r="B62" t="s">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B63" t="s">
         <v>124</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C63" t="s">
         <v>125</v>
       </c>
-      <c r="D62" s="4">
+      <c r="D63" s="4">
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
-      <c r="B63" t="s">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B64" t="s">
         <v>126</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C64" t="s">
         <v>127</v>
       </c>
-      <c r="D63" s="4">
+      <c r="D64" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
-      <c r="B64" t="s">
+    <row r="65" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B65" t="s">
         <v>128</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C65" t="s">
         <v>129</v>
       </c>
-      <c r="D64" s="4">
+      <c r="D65" s="4">
         <v>0.4</v>
       </c>
     </row>
-    <row r="65" spans="2:4">
-      <c r="B65" t="s">
+    <row r="66" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B66" t="s">
         <v>130</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C66" t="s">
         <v>131</v>
       </c>
-      <c r="D65" s="4">
+      <c r="D66" s="4">
         <v>0.8</v>
       </c>
     </row>
-    <row r="66" spans="2:4">
-      <c r="B66" t="s">
+    <row r="67" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B67" t="s">
         <v>132</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C67" t="s">
         <v>133</v>
       </c>
-      <c r="D66" s="4">
+      <c r="D67" s="4">
         <v>0.7</v>
       </c>
     </row>
-    <row r="67" spans="2:4">
-      <c r="B67" t="s">
+    <row r="68" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B68" t="s">
         <v>134</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C68" t="s">
         <v>135</v>
-      </c>
-      <c r="D67" s="5">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="68" spans="2:4">
-      <c r="B68" t="s">
-        <v>136</v>
-      </c>
-      <c r="C68" t="s">
-        <v>137</v>
       </c>
       <c r="D68" s="5">
         <v>0.2</v>
       </c>
     </row>
-    <row r="69" spans="2:4">
+    <row r="69" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
+        <v>136</v>
+      </c>
+      <c r="C69" t="s">
+        <v>137</v>
+      </c>
+      <c r="D69" s="5">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B70" t="s">
         <v>138</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C70" t="s">
         <v>139</v>
-      </c>
-      <c r="D69" s="5">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="70" spans="2:4">
-      <c r="B70" t="s">
-        <v>140</v>
-      </c>
-      <c r="C70" t="s">
-        <v>141</v>
       </c>
       <c r="D70" s="5">
         <v>0.6</v>
       </c>
     </row>
-    <row r="71" spans="2:4">
+    <row r="71" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C71" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D71" s="5">
         <v>0.6</v>
       </c>
     </row>
-    <row r="72" spans="2:4">
+    <row r="72" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
+        <v>142</v>
+      </c>
+      <c r="C72" t="s">
+        <v>143</v>
+      </c>
+      <c r="D72" s="5">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="73" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B73" t="s">
         <v>144</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C73" t="s">
         <v>145</v>
       </c>
-      <c r="D72" s="5">
+      <c r="D73" s="5">
         <v>0.7</v>
       </c>
     </row>
-    <row r="73" spans="2:4">
-      <c r="B73" t="s">
+    <row r="74" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B74" t="s">
         <v>146</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C74" t="s">
         <v>147</v>
       </c>
-      <c r="D73" s="4">
+      <c r="D74" s="4">
         <v>100</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\Avenge\AAAGameData\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9B7966B-4186-4F2A-BC27-7676603DAEE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="10480"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -29,12 +30,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="154">
   <si>
     <t>#</t>
   </si>
@@ -489,20 +493,21 @@
     <t>VisionBoundaryFadeDistance</t>
   </si>
   <si>
-    <t>视野边界向较透明侧延伸的过渡距离（世界单位）</t>
+    <t>视野边界向较透明侧延伸的过渡距离（Fog逻辑格）</t>
+  </si>
+  <si>
+    <t>FogLogicCellSize</t>
+  </si>
+  <si>
+    <t>Fog逻辑格边长（世界单位）</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -516,346 +521,16 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -863,326 +538,40 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1432,20 +821,20 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D75"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D76"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="33.3636363636364" style="1" customWidth="1"/>
-    <col min="3" max="3" width="36.3636363636364" style="1" customWidth="1"/>
+    <col min="2" max="2" width="33.36328125" customWidth="1" style="1"/>
+    <col min="3" max="3" width="36.36328125" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1455,7 +844,7 @@
       <c r="C1" s="3"/>
       <c r="D1" s="4"/>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1469,7 +858,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
         <v>5</v>
@@ -1481,7 +870,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
         <v>7</v>
@@ -1493,7 +882,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
         <v>9</v>
@@ -1505,7 +894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
         <v>11</v>
@@ -1517,7 +906,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
         <v>13</v>
@@ -1529,7 +918,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
         <v>15</v>
@@ -1541,7 +930,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
         <v>17</v>
@@ -1553,7 +942,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
         <v>19</v>
@@ -1565,7 +954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
         <v>21</v>
@@ -1577,7 +966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
         <v>23</v>
@@ -1589,7 +978,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
         <v>25</v>
@@ -1601,7 +990,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
         <v>27</v>
@@ -1613,7 +1002,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
         <v>29</v>
@@ -1625,7 +1014,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
         <v>31</v>
@@ -1637,7 +1026,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
         <v>33</v>
@@ -1649,7 +1038,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
         <v>35</v>
@@ -1661,7 +1050,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
         <v>37</v>
@@ -1673,7 +1062,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
         <v>39</v>
@@ -1685,41 +1074,41 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
-      <c r="B21" t="s">
+    <row r="21">
+      <c r="B21" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D21" s="5">
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
-      <c r="B22" t="s">
+    <row r="22">
+      <c r="B22" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D22" s="5">
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
-      <c r="B23" t="s">
+    <row r="23">
+      <c r="B23" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D23" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
-      <c r="B24" t="s">
+    <row r="24">
+      <c r="B24" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C24" s="6" t="s">
@@ -1729,30 +1118,30 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
-      <c r="B25" t="s">
+    <row r="25">
+      <c r="B25" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D25" s="5">
         <v>5.4</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
-      <c r="B26" t="s">
+    <row r="26">
+      <c r="B26" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D26" s="5">
         <v>8.1</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
-      <c r="B27" t="s">
+    <row r="27">
+      <c r="B27" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C27" s="6" t="s">
@@ -1762,30 +1151,30 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
-      <c r="B28" t="s">
+    <row r="28">
+      <c r="B28" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="1" t="s">
         <v>56</v>
       </c>
       <c r="D28" s="5">
         <v>14.4</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
-      <c r="B29" t="s">
+    <row r="29">
+      <c r="B29" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D29" s="5">
         <v>54</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
-      <c r="B30" t="s">
+    <row r="30">
+      <c r="B30" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C30" s="6" t="s">
@@ -1795,505 +1184,517 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
-      <c r="B31" t="s">
+    <row r="31">
+      <c r="B31" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D31" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
-      <c r="B32" t="s">
+    <row r="32">
+      <c r="B32" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D32" s="5">
         <v>7.2</v>
       </c>
     </row>
-    <row r="33" spans="2:4">
-      <c r="B33" t="s">
+    <row r="33">
+      <c r="B33" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="1" t="s">
         <v>66</v>
       </c>
       <c r="D33" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="2:4">
-      <c r="B34" t="s">
+    <row r="34">
+      <c r="B34" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D34" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="2:4">
-      <c r="B35" t="s">
+    <row r="35">
+      <c r="B35" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="1" t="s">
         <v>70</v>
       </c>
       <c r="D35" s="5">
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="2:4">
-      <c r="B36" t="s">
+    <row r="36">
+      <c r="B36" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D36" s="5">
         <v>0.5</v>
       </c>
     </row>
-    <row r="37" spans="2:4">
-      <c r="B37" t="s">
+    <row r="37">
+      <c r="B37" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="1" t="s">
         <v>74</v>
       </c>
       <c r="D37" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="2:4">
-      <c r="B38" t="s">
+    <row r="38">
+      <c r="B38" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D38" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="2:4">
-      <c r="B39" t="s">
+    <row r="39">
+      <c r="B39" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D39" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="2:4">
-      <c r="B40" t="s">
+    <row r="40">
+      <c r="B40" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D40" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="2:4">
-      <c r="B41" t="s">
+    <row r="41">
+      <c r="B41" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D41" s="5">
         <v>0.01</v>
       </c>
     </row>
-    <row r="42" spans="2:4">
-      <c r="B42" t="s">
+    <row r="42">
+      <c r="B42" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D42" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="2:4">
-      <c r="B43" t="s">
+    <row r="43">
+      <c r="B43" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="1" t="s">
         <v>86</v>
       </c>
       <c r="D43" s="5">
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="2:4">
-      <c r="B44" t="s">
+    <row r="44">
+      <c r="B44" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D44" s="5">
         <v>24</v>
       </c>
     </row>
-    <row r="45" spans="2:4">
-      <c r="B45" t="s">
+    <row r="45">
+      <c r="B45" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D45" s="5">
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="2:4">
-      <c r="B46" t="s">
+    <row r="46">
+      <c r="B46" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="1" t="s">
         <v>92</v>
       </c>
       <c r="D46" s="5">
         <v>32</v>
       </c>
     </row>
-    <row r="47" spans="2:4">
-      <c r="B47" t="s">
+    <row r="47">
+      <c r="B47" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="1" t="s">
         <v>94</v>
       </c>
       <c r="D47" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="2:4">
-      <c r="B48" t="s">
+    <row r="48">
+      <c r="B48" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D48" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
-      <c r="B49" t="s">
+    <row r="49">
+      <c r="B49" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="1" t="s">
         <v>98</v>
       </c>
       <c r="D49" s="5">
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
-      <c r="B50" t="s">
+    <row r="50">
+      <c r="B50" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="1" t="s">
         <v>100</v>
       </c>
       <c r="D50" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
-      <c r="B51" t="s">
+    <row r="51">
+      <c r="B51" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="1" t="s">
         <v>102</v>
       </c>
       <c r="D51" s="5">
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
-      <c r="B52" t="s">
+    <row r="52">
+      <c r="B52" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="1" t="s">
         <v>104</v>
       </c>
       <c r="D52" s="5">
         <v>32</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
-      <c r="B53" t="s">
+    <row r="53">
+      <c r="B53" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="1" t="s">
         <v>106</v>
       </c>
       <c r="D53" s="5">
         <v>20</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
-      <c r="B54" t="s">
+    <row r="54">
+      <c r="B54" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" s="1" t="s">
         <v>108</v>
       </c>
       <c r="D54" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
-      <c r="B55" t="s">
+    <row r="55">
+      <c r="B55" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="1" t="s">
         <v>110</v>
       </c>
       <c r="D55" s="5">
         <v>50</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
-      <c r="B56" t="s">
+    <row r="56">
+      <c r="B56" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" s="1" t="s">
         <v>112</v>
       </c>
       <c r="D56" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
-      <c r="B57" t="s">
+    <row r="57">
+      <c r="B57" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C57" s="1" t="s">
         <v>114</v>
       </c>
       <c r="D57" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
-      <c r="B58" t="s">
+    <row r="58">
+      <c r="B58" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="1" t="s">
         <v>116</v>
       </c>
       <c r="D58" s="5">
         <v>3.5</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
-      <c r="B59" t="s">
+    <row r="59">
+      <c r="B59" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" s="1" t="s">
         <v>118</v>
       </c>
       <c r="D59" s="5">
         <v>1.2</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
-      <c r="B60" t="s">
+    <row r="60">
+      <c r="B60" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="1" t="s">
         <v>120</v>
       </c>
       <c r="D60" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
-      <c r="B61" t="s">
+    <row r="61">
+      <c r="B61" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="1" t="s">
         <v>122</v>
       </c>
       <c r="D61" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:4">
-      <c r="A62" t="s">
+    <row r="62">
+      <c r="A62" s="0" t="s">
         <v>123</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="1" t="s">
         <v>125</v>
       </c>
       <c r="D62" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
-      <c r="B63" t="s">
+    <row r="63">
+      <c r="B63" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="1" t="s">
         <v>127</v>
       </c>
       <c r="D63" s="5">
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
-      <c r="B64" t="s">
+    <row r="64">
+      <c r="B64" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" s="1" t="s">
         <v>129</v>
       </c>
       <c r="D64" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="2:4">
-      <c r="B65" t="s">
+    <row r="65">
+      <c r="B65" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" s="1" t="s">
         <v>131</v>
       </c>
       <c r="D65" s="5">
         <v>0.4</v>
       </c>
     </row>
-    <row r="66" spans="2:4">
-      <c r="B66" t="s">
+    <row r="66">
+      <c r="B66" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C66" s="1" t="s">
         <v>133</v>
       </c>
       <c r="D66" s="5">
         <v>0.8</v>
       </c>
     </row>
-    <row r="67" spans="2:4">
-      <c r="B67" t="s">
+    <row r="67">
+      <c r="B67" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C67" s="1" t="s">
         <v>135</v>
       </c>
       <c r="D67" s="5">
         <v>0.7</v>
       </c>
     </row>
-    <row r="68" spans="2:4">
-      <c r="B68" t="s">
+    <row r="68">
+      <c r="B68" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C68" s="1" t="s">
         <v>137</v>
       </c>
       <c r="D68" s="5">
         <v>0.2</v>
       </c>
     </row>
-    <row r="69" spans="2:4">
-      <c r="B69" t="s">
+    <row r="69">
+      <c r="B69" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C69" s="1" t="s">
         <v>139</v>
       </c>
       <c r="D69" s="5">
         <v>0.2</v>
       </c>
     </row>
-    <row r="70" spans="2:4">
-      <c r="B70" t="s">
+    <row r="70">
+      <c r="B70" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C70" s="1" t="s">
         <v>141</v>
       </c>
       <c r="D70" s="5">
         <v>0.6</v>
       </c>
     </row>
-    <row r="71" spans="2:4">
-      <c r="B71" t="s">
+    <row r="71">
+      <c r="B71" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C71" s="1" t="s">
         <v>143</v>
       </c>
       <c r="D71" s="5">
         <v>0.6</v>
       </c>
     </row>
-    <row r="72" spans="2:4">
-      <c r="B72" t="s">
+    <row r="72">
+      <c r="B72" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C72" s="1" t="s">
         <v>145</v>
       </c>
       <c r="D72" s="5">
         <v>0.6</v>
       </c>
     </row>
-    <row r="73" spans="2:4">
-      <c r="B73" t="s">
+    <row r="73">
+      <c r="B73" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C73" s="1" t="s">
         <v>147</v>
       </c>
       <c r="D73" s="5">
         <v>0.7</v>
       </c>
     </row>
-    <row r="74" spans="2:4">
-      <c r="B74" t="s">
+    <row r="74">
+      <c r="B74" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C74" s="1" t="s">
         <v>149</v>
       </c>
       <c r="D74" s="5">
         <v>100</v>
       </c>
     </row>
-    <row r="75" spans="2:4">
-      <c r="B75" t="s">
+    <row r="75">
+      <c r="B75" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C75" s="1" t="s">
         <v>151</v>
       </c>
       <c r="D75" s="5">
-        <v>0.5</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D76" s="5">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -2301,11 +1702,10 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -2313,11 +1713,10 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\Avenge\AAAGameData\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9B7966B-4186-4F2A-BC27-7676603DAEE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="25600" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -30,15 +29,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="154">
   <si>
     <t>#</t>
   </si>
@@ -493,7 +489,7 @@
     <t>VisionBoundaryFadeDistance</t>
   </si>
   <si>
-    <t>视野边界向较透明侧延伸的过渡距离（Fog逻辑格）</t>
+    <t>视野边界向较透明侧延伸的过渡距离（世界单位）</t>
   </si>
   <si>
     <t>FogLogicCellSize</t>
@@ -505,9 +501,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -521,16 +522,346 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -538,40 +869,326 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -821,20 +1438,20 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D76"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
-    <col min="2" max="2" width="33.36328125" customWidth="1" style="1"/>
-    <col min="3" max="3" width="36.36328125" customWidth="1" style="1"/>
+    <col min="2" max="2" width="33.3636363636364" style="1" customWidth="1"/>
+    <col min="3" max="3" width="36.3636363636364" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -844,7 +1461,7 @@
       <c r="C1" s="3"/>
       <c r="D1" s="4"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -858,7 +1475,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
         <v>5</v>
@@ -870,7 +1487,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:4">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
         <v>7</v>
@@ -882,7 +1499,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:4">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
         <v>9</v>
@@ -894,7 +1511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:4">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
         <v>11</v>
@@ -906,7 +1523,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:4">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
         <v>13</v>
@@ -918,7 +1535,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:4">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
         <v>15</v>
@@ -930,7 +1547,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:4">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
         <v>17</v>
@@ -942,7 +1559,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:4">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
         <v>19</v>
@@ -954,7 +1571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:4">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
         <v>21</v>
@@ -966,7 +1583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:4">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
         <v>23</v>
@@ -978,7 +1595,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:4">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
         <v>25</v>
@@ -990,7 +1607,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:4">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
         <v>27</v>
@@ -1002,7 +1619,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:4">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
         <v>29</v>
@@ -1014,7 +1631,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:4">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
         <v>31</v>
@@ -1026,7 +1643,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:4">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
         <v>33</v>
@@ -1038,7 +1655,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:4">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
         <v>35</v>
@@ -1050,7 +1667,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:4">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
         <v>37</v>
@@ -1062,7 +1679,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:4">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
         <v>39</v>
@@ -1074,7 +1691,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:4">
       <c r="B21" s="1" t="s">
         <v>41</v>
       </c>
@@ -1085,7 +1702,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:4">
       <c r="B22" s="1" t="s">
         <v>43</v>
       </c>
@@ -1096,7 +1713,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:4">
       <c r="B23" s="1" t="s">
         <v>45</v>
       </c>
@@ -1107,7 +1724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:4">
       <c r="B24" s="1" t="s">
         <v>47</v>
       </c>
@@ -1118,7 +1735,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:4">
       <c r="B25" s="1" t="s">
         <v>49</v>
       </c>
@@ -1129,7 +1746,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:4">
       <c r="B26" s="1" t="s">
         <v>51</v>
       </c>
@@ -1140,7 +1757,7 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:4">
       <c r="B27" s="1" t="s">
         <v>53</v>
       </c>
@@ -1151,7 +1768,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:4">
       <c r="B28" s="1" t="s">
         <v>55</v>
       </c>
@@ -1162,7 +1779,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:4">
       <c r="B29" s="1" t="s">
         <v>57</v>
       </c>
@@ -1173,7 +1790,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:4">
       <c r="B30" s="1" t="s">
         <v>59</v>
       </c>
@@ -1184,7 +1801,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:4">
       <c r="B31" s="1" t="s">
         <v>61</v>
       </c>
@@ -1195,7 +1812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:4">
       <c r="B32" s="1" t="s">
         <v>63</v>
       </c>
@@ -1206,7 +1823,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="2:4">
       <c r="B33" s="1" t="s">
         <v>65</v>
       </c>
@@ -1217,7 +1834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="2:4">
       <c r="B34" s="1" t="s">
         <v>67</v>
       </c>
@@ -1228,7 +1845,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="2:4">
       <c r="B35" s="1" t="s">
         <v>69</v>
       </c>
@@ -1239,7 +1856,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="2:4">
       <c r="B36" s="1" t="s">
         <v>71</v>
       </c>
@@ -1250,7 +1867,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="2:4">
       <c r="B37" s="1" t="s">
         <v>73</v>
       </c>
@@ -1261,7 +1878,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="2:4">
       <c r="B38" s="1" t="s">
         <v>75</v>
       </c>
@@ -1272,7 +1889,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="2:4">
       <c r="B39" s="1" t="s">
         <v>77</v>
       </c>
@@ -1283,7 +1900,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="2:4">
       <c r="B40" s="1" t="s">
         <v>79</v>
       </c>
@@ -1294,7 +1911,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="2:4">
       <c r="B41" s="1" t="s">
         <v>81</v>
       </c>
@@ -1305,7 +1922,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="2:4">
       <c r="B42" s="1" t="s">
         <v>83</v>
       </c>
@@ -1316,7 +1933,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="2:4">
       <c r="B43" s="1" t="s">
         <v>85</v>
       </c>
@@ -1327,7 +1944,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="2:4">
       <c r="B44" s="1" t="s">
         <v>87</v>
       </c>
@@ -1338,7 +1955,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="2:4">
       <c r="B45" s="1" t="s">
         <v>89</v>
       </c>
@@ -1349,7 +1966,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="2:4">
       <c r="B46" s="1" t="s">
         <v>91</v>
       </c>
@@ -1360,7 +1977,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="2:4">
       <c r="B47" s="1" t="s">
         <v>93</v>
       </c>
@@ -1371,7 +1988,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="2:4">
       <c r="B48" s="1" t="s">
         <v>95</v>
       </c>
@@ -1382,7 +1999,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:4">
       <c r="B49" s="1" t="s">
         <v>97</v>
       </c>
@@ -1393,7 +2010,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:4">
       <c r="B50" s="1" t="s">
         <v>99</v>
       </c>
@@ -1404,7 +2021,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:4">
       <c r="B51" s="1" t="s">
         <v>101</v>
       </c>
@@ -1415,7 +2032,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:4">
       <c r="B52" s="1" t="s">
         <v>103</v>
       </c>
@@ -1426,7 +2043,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:4">
       <c r="B53" s="1" t="s">
         <v>105</v>
       </c>
@@ -1437,7 +2054,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:4">
       <c r="B54" s="1" t="s">
         <v>107</v>
       </c>
@@ -1448,7 +2065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:4">
       <c r="B55" s="1" t="s">
         <v>109</v>
       </c>
@@ -1459,7 +2076,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:4">
       <c r="B56" s="1" t="s">
         <v>111</v>
       </c>
@@ -1470,7 +2087,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:4">
       <c r="B57" s="1" t="s">
         <v>113</v>
       </c>
@@ -1481,7 +2098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:4">
       <c r="B58" s="1" t="s">
         <v>115</v>
       </c>
@@ -1492,7 +2109,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:4">
       <c r="B59" s="1" t="s">
         <v>117</v>
       </c>
@@ -1503,7 +2120,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:4">
       <c r="B60" s="1" t="s">
         <v>119</v>
       </c>
@@ -1514,7 +2131,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:4">
       <c r="B61" s="1" t="s">
         <v>121</v>
       </c>
@@ -1525,8 +2142,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="0" t="s">
+    <row r="62" spans="1:4">
+      <c r="A62" t="s">
         <v>123</v>
       </c>
       <c r="B62" s="1" t="s">
@@ -1539,7 +2156,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:4">
       <c r="B63" s="1" t="s">
         <v>126</v>
       </c>
@@ -1550,7 +2167,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:4">
       <c r="B64" s="1" t="s">
         <v>128</v>
       </c>
@@ -1561,7 +2178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="2:4">
       <c r="B65" s="1" t="s">
         <v>130</v>
       </c>
@@ -1572,7 +2189,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="2:4">
       <c r="B66" s="1" t="s">
         <v>132</v>
       </c>
@@ -1583,7 +2200,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="2:4">
       <c r="B67" s="1" t="s">
         <v>134</v>
       </c>
@@ -1594,7 +2211,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="2:4">
       <c r="B68" s="1" t="s">
         <v>136</v>
       </c>
@@ -1605,7 +2222,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="2:4">
       <c r="B69" s="1" t="s">
         <v>138</v>
       </c>
@@ -1616,7 +2233,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="2:4">
       <c r="B70" s="1" t="s">
         <v>140</v>
       </c>
@@ -1627,7 +2244,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="2:4">
       <c r="B71" s="1" t="s">
         <v>142</v>
       </c>
@@ -1638,7 +2255,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="2:4">
       <c r="B72" s="1" t="s">
         <v>144</v>
       </c>
@@ -1649,7 +2266,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="2:4">
       <c r="B73" s="1" t="s">
         <v>146</v>
       </c>
@@ -1660,7 +2277,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="2:4">
       <c r="B74" s="1" t="s">
         <v>148</v>
       </c>
@@ -1671,7 +2288,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="2:4">
       <c r="B75" s="1" t="s">
         <v>150</v>
       </c>
@@ -1682,7 +2299,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="2:4">
       <c r="B76" s="1" t="s">
         <v>152</v>
       </c>
@@ -1694,7 +2311,6 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -1702,10 +2318,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -1713,10 +2330,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -2296,7 +2296,7 @@
         <v>151</v>
       </c>
       <c r="D75" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="2:4">
